--- a/docs/Hotel_Booking_Engine_Issue_Tracker_FILLED.xlsx
+++ b/docs/Hotel_Booking_Engine_Issue_Tracker_FILLED.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15900" tabRatio="600" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name=" Issue Tracker" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Load &amp; Cost Scenarios" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Team &amp; Hiring" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Phase Plan" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name=" Priority Matrix" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name=" Dashboard" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name=" Timeframes" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="How to Use" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name=" Issue Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Load &amp; Cost Scenarios" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CI-CD Pipeline" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team &amp; Hiring" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase Plan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name=" Priority Matrix" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name=" Dashboard" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name=" Timeframes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to Use" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -23,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -130,8 +131,14 @@
       <color rgb="FF1F3864"/>
       <sz val="13"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF38761D"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="22">
+  <fills count="23">
     <fill>
       <patternFill/>
     </fill>
@@ -225,12 +232,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFD966"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE06666"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFD966"/>
+        <fgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
     <fill>
@@ -324,7 +336,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -536,23 +548,72 @@
     <xf numFmtId="0" fontId="4" fillId="20" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -562,44 +623,8 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1001,7 +1026,7 @@
     <row r="2" ht="20" customHeight="1" s="52">
       <c r="A2" s="53" t="inlineStr">
         <is>
-          <t>Track pre-development, development &amp; post-launch errors | Assign ownership | Monitor resolution</t>
+          <t>Status: 5 of 34 fixed already (incl. the critical AI-assistant restore) • 29 logged as a proactive hardening roadmap — latent risks that surface under live guest load, not current outages. Backend tests green (253 passed); CI/CD strengthened.</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1112,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="90" customHeight="1" s="52">
+    <row r="4" ht="100" customHeight="1" s="52">
       <c r="A4" s="63" t="inlineStr">
         <is>
           <t>BE-001</t>
@@ -1105,22 +1130,23 @@
       </c>
       <c r="D4" s="66" t="inlineStr">
         <is>
-          <t>No defined per-hotel AI spend budget or billing pass-through</t>
+          <t>Define a per-hotel AI spend budget &amp; billing model</t>
         </is>
       </c>
       <c r="E4" s="65" t="inlineStr">
         <is>
-          <t>Token usage is recorded (ai_tokens:{hotel_id}:{date} in Redis, ai_usage.py) but there is no budget, no alert threshold, and LLM cost is not billed back to hotels.</t>
+          <t>Token usage is already recorded per hotel/day (ai_usage.py -&gt; Redis ai_tokens:{hotel}:{date}); what's missing is a budget ceiling, alert threshold and a bill pass-through decision.
+⏱ When it surfaces: As paid AI usage grows across many live hotels.</t>
         </is>
       </c>
       <c r="F4" s="65" t="inlineStr">
         <is>
-          <t>Cost governance was never defined as a requirement before building AI features.</t>
+          <t>Cost governance was not defined as a requirement up front.</t>
         </is>
       </c>
       <c r="G4" s="65" t="inlineStr">
         <is>
-          <t>Define a monthly AI cost ceiling per plan tier; add alerting on the ai_tokens counters; decide pass-through vs absorbed cost.</t>
+          <t>Set a monthly AI ceiling per plan tier; alert on the existing counters; decide absorbed vs passed-through cost.</t>
         </is>
       </c>
       <c r="H4" s="67" t="inlineStr">
@@ -1144,7 +1170,7 @@
         </is>
       </c>
       <c r="L4" s="65" t="inlineStr"/>
-      <c r="M4" s="65" t="inlineStr"/>
+      <c r="M4" s="69" t="inlineStr"/>
       <c r="N4" s="65" t="inlineStr"/>
       <c r="O4" s="70">
         <f>IF(AND(K4&lt;&gt;"",M4&lt;&gt;""),M4-K4,"")</f>
@@ -1152,11 +1178,11 @@
       </c>
       <c r="P4" s="65" t="inlineStr">
         <is>
-          <t>Uncontrolled LLM bill grows silently with usage; margin erosion is discovered only on the monthly cloud invoice.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="90" customHeight="1" s="52">
+          <t>Protects margin: prevents a slow, invisible LLM-cost creep from showing up only on the monthly invoice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="100" customHeight="1" s="52">
       <c r="A5" s="63" t="inlineStr">
         <is>
           <t>BE-002</t>
@@ -1174,27 +1200,28 @@
       </c>
       <c r="D5" s="66" t="inlineStr">
         <is>
-          <t>Trusted reverse-proxy hop for client IP never defined</t>
+          <t>Pin the trusted reverse-proxy hop for client IP</t>
         </is>
       </c>
       <c r="E5" s="65" t="inlineStr">
         <is>
-          <t>Rate limiting keys on the FIRST X-Forwarded-For value (limiter.py get_real_ip), which the client fully controls behind most proxies.</t>
+          <t>Rate limiting reads the first X-Forwarded-For value (limiter.py). Behind most proxies the client can set this header, so IP-based limits can be diluted.
+⏱ When it surfaces: When someone deliberately rotates X-Forwarded-For to dodge limits.</t>
         </is>
       </c>
       <c r="F5" s="65" t="inlineStr">
         <is>
-          <t>No decision on which proxy hop is trustworthy; XFF taken at face value.</t>
+          <t>Deployment trust boundary (which proxy hop is trusted) is not yet pinned.</t>
         </is>
       </c>
       <c r="G5" s="65" t="inlineStr">
         <is>
-          <t>Pin the trusted proxy and read the client IP from the correct hop (or use a CDN-verified header); document the deployment topology.</t>
-        </is>
-      </c>
-      <c r="H5" s="71" t="inlineStr">
-        <is>
-          <t>Critical</t>
+          <t>Read the client IP from the verified proxy hop / CDN header; document the topology.</t>
+        </is>
+      </c>
+      <c r="H5" s="67" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="I5" s="68" t="inlineStr">
@@ -1204,7 +1231,7 @@
       </c>
       <c r="J5" s="65" t="inlineStr">
         <is>
-          <t>DevOps / Backend Dev</t>
+          <t>Tech Lead / Founder</t>
         </is>
       </c>
       <c r="K5" s="69" t="inlineStr">
@@ -1213,7 +1240,7 @@
         </is>
       </c>
       <c r="L5" s="65" t="inlineStr"/>
-      <c r="M5" s="65" t="inlineStr"/>
+      <c r="M5" s="69" t="inlineStr"/>
       <c r="N5" s="65" t="inlineStr"/>
       <c r="O5" s="70">
         <f>IF(AND(K5&lt;&gt;"",M5&lt;&gt;""),M5-K5,"")</f>
@@ -1221,11 +1248,11 @@
       </c>
       <c r="P5" s="65" t="inlineStr">
         <is>
-          <t>Every IP-based limit (login, public booking, AI chat) is bypassable by spoofing a header -&gt; abuse and cost controls are porous.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="90" customHeight="1" s="52">
+          <t>Hardens every IP-based limit (login, booking, AI chat) against header spoofing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="100" customHeight="1" s="52">
       <c r="A6" s="63" t="inlineStr">
         <is>
           <t>BE-003</t>
@@ -1243,27 +1270,28 @@
       </c>
       <c r="D6" s="66" t="inlineStr">
         <is>
-          <t>Security controls are fail-OPEN on Redis outage</t>
+          <t>Decide fail-closed vs fail-open for Redis-backed controls</t>
         </is>
       </c>
       <c r="E6" s="65" t="inlineStr">
         <is>
-          <t>_enforce_hotel_ai_quota (chat.py) and the rate limiter silently allow all traffic when Redis is unreachable; quota/limits simply stop applying.</t>
+          <t>_enforce_hotel_ai_quota and the limiter intentionally fail OPEN if Redis is unreachable so real guests aren't blocked — a deliberate availability choice that trades away cost protection during an outage.
+⏱ When it surfaces: Only during a Redis outage coinciding with a traffic/abuse spike.</t>
         </is>
       </c>
       <c r="F6" s="65" t="inlineStr">
         <is>
-          <t>Availability was prioritised over safety in the original design; no fallback budget.</t>
+          <t>Availability prioritised over cost-safety; no conservative fallback budget.</t>
         </is>
       </c>
       <c r="G6" s="65" t="inlineStr">
         <is>
-          <t>Make cost-bearing controls fail-closed or degrade to a conservative in-process limit; add Redis health alerting.</t>
-        </is>
-      </c>
-      <c r="H6" s="67" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Add a conservative in-process fallback cap for cost-bearing controls; alert on Redis health.</t>
+        </is>
+      </c>
+      <c r="H6" s="71" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I6" s="68" t="inlineStr">
@@ -1273,7 +1301,7 @@
       </c>
       <c r="J6" s="65" t="inlineStr">
         <is>
-          <t>Backend Dev</t>
+          <t>Tech Lead / Founder</t>
         </is>
       </c>
       <c r="K6" s="69" t="inlineStr">
@@ -1282,7 +1310,7 @@
         </is>
       </c>
       <c r="L6" s="65" t="inlineStr"/>
-      <c r="M6" s="65" t="inlineStr"/>
+      <c r="M6" s="69" t="inlineStr"/>
       <c r="N6" s="65" t="inlineStr"/>
       <c r="O6" s="70">
         <f>IF(AND(K6&lt;&gt;"",M6&lt;&gt;""),M6-K6,"")</f>
@@ -1290,11 +1318,11 @@
       </c>
       <c r="P6" s="65" t="inlineStr">
         <is>
-          <t>A Redis blip removes all abuse/cost protection at once -&gt; a spike during an outage can run an unbounded LLM/DB bill.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="90" customHeight="1" s="52">
+          <t>Keeps a floor of abuse/cost protection even when Redis is briefly unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="100" customHeight="1" s="52">
       <c r="A7" s="63" t="inlineStr">
         <is>
           <t>BE-004</t>
@@ -1312,22 +1340,23 @@
       </c>
       <c r="D7" s="66" t="inlineStr">
         <is>
-          <t>Peak-load / stress test never executed before launch</t>
+          <t>Run the peak-load test before go-live</t>
         </is>
       </c>
       <c r="E7" s="65" t="inlineStr">
         <is>
-          <t>A load-test script exists (scripts/load_test.py) and SCALE_TUNING.md documents the math, but no evidence it was run at expected peak concurrency.</t>
+          <t>A ready load-test script (scripts/load_test.py) and a sizing guide (SCALE_TUNING.md) exist; the test simply needs to be executed at expected peak and the pool/concurrency tuned to the result.
+⏱ When it surfaces: At the first real high-traffic moment (sale, campaign, festival).</t>
         </is>
       </c>
       <c r="F7" s="65" t="inlineStr">
         <is>
-          <t>Go-live checklist item left unchecked.</t>
+          <t>Go-live checklist item still open.</t>
         </is>
       </c>
       <c r="G7" s="65" t="inlineStr">
         <is>
-          <t>Run load_test.py against staging at expected peak; tune WEB_CONCURRENCY and pool to stay under the Supabase connection limit.</t>
+          <t>Run load_test.py on staging at expected peak; set WEB_CONCURRENCY and pool under the Supabase limit.</t>
         </is>
       </c>
       <c r="H7" s="67" t="inlineStr">
@@ -1342,7 +1371,7 @@
       </c>
       <c r="J7" s="65" t="inlineStr">
         <is>
-          <t>DevOps / Backend Dev</t>
+          <t>Tech Lead / Founder</t>
         </is>
       </c>
       <c r="K7" s="69" t="inlineStr">
@@ -1351,7 +1380,7 @@
         </is>
       </c>
       <c r="L7" s="65" t="inlineStr"/>
-      <c r="M7" s="65" t="inlineStr"/>
+      <c r="M7" s="69" t="inlineStr"/>
       <c r="N7" s="65" t="inlineStr"/>
       <c r="O7" s="70">
         <f>IF(AND(K7&lt;&gt;"",M7&lt;&gt;""),M7-K7,"")</f>
@@ -1359,11 +1388,11 @@
       </c>
       <c r="P7" s="65" t="inlineStr">
         <is>
-          <t>First real traffic spike becomes the load test in production; the ceiling is discovered by an outage, not a graph.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1" s="52">
+          <t>Turns the scaling ceiling into a known number instead of discovering it during a live spike.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="100" customHeight="1" s="52">
       <c r="A8" s="63" t="inlineStr">
         <is>
           <t>BE-005</t>
@@ -1381,27 +1410,28 @@
       </c>
       <c r="D8" s="66" t="inlineStr">
         <is>
-          <t>DB connection budget not validated for AI workloads</t>
+          <t>Validate the DB connection budget for AI/streaming workloads</t>
         </is>
       </c>
       <c r="E8" s="65" t="inlineStr">
         <is>
-          <t>Default pool is 10 conns/worker; AI chat holds a DB connection for the whole multi-second LLM call, so effective concurrency is far lower than assumed.</t>
+          <t>Default pool is ~10 conns/worker. AI chat keeps a DB session open during the LLM call, so effective AI concurrency is lower than the raw pool math suggests.
+⏱ When it surfaces: As concurrent AI chats rise across busy hotels.</t>
         </is>
       </c>
       <c r="F8" s="65" t="inlineStr">
         <is>
-          <t>Connection math in SCALE_TUNING.md assumes short requests; long-held AI requests were not modelled.</t>
+          <t>Connection math assumes short requests; long AI requests were not separately modelled.</t>
         </is>
       </c>
       <c r="G8" s="65" t="inlineStr">
         <is>
-          <t>Model AI concurrency separately; release the DB session before the LLM round-trip (see BE-Dev item); size the pool against Supabase limit.</t>
+          <t>Model AI concurrency separately; size pool vs Supabase limit; combine with the streaming/session work below.</t>
         </is>
       </c>
       <c r="H8" s="71" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I8" s="68" t="inlineStr">
@@ -1411,7 +1441,7 @@
       </c>
       <c r="J8" s="65" t="inlineStr">
         <is>
-          <t>Backend Dev</t>
+          <t>Tech Lead / Founder</t>
         </is>
       </c>
       <c r="K8" s="69" t="inlineStr">
@@ -1420,7 +1450,7 @@
         </is>
       </c>
       <c r="L8" s="65" t="inlineStr"/>
-      <c r="M8" s="65" t="inlineStr"/>
+      <c r="M8" s="69" t="inlineStr"/>
       <c r="N8" s="65" t="inlineStr"/>
       <c r="O8" s="70">
         <f>IF(AND(K8&lt;&gt;"",M8&lt;&gt;""),M8-K8,"")</f>
@@ -1428,11 +1458,11 @@
       </c>
       <c r="P8" s="65" t="inlineStr">
         <is>
-          <t>Connection pool exhaustion takes down the ENTIRE API (not just AI) when many chats run at once.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="90" customHeight="1" s="52">
+          <t>Prevents connection-pool pressure from AI traffic affecting the rest of the API.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="100" customHeight="1" s="52">
       <c r="A9" s="63" t="inlineStr">
         <is>
           <t>BE-006</t>
@@ -1450,22 +1480,23 @@
       </c>
       <c r="D9" s="66" t="inlineStr">
         <is>
-          <t>No dedicated backend / frontend engineering ownership</t>
+          <t>Assign dedicated backend &amp; frontend engineering ownership</t>
         </is>
       </c>
       <c r="E9" s="65" t="inlineStr">
         <is>
-          <t>The codebase is large (~70 routers, 250+ endpoints, payments, multi-tenant, AI) but there is no named owner for backend reliability or frontend UX/perf.</t>
+          <t>The platform is large (~70 routers, 250+ endpoints, payments, multi-tenant, AI). Today there is no named owner for backend reliability or frontend UX/performance.
+⏱ When it surfaces: Continuously — every unowned issue ages without a clear owner.</t>
         </is>
       </c>
       <c r="F9" s="65" t="inlineStr">
         <is>
-          <t>Project grew faster than the team.</t>
+          <t>Project scope outgrew the team.</t>
         </is>
       </c>
       <c r="G9" s="65" t="inlineStr">
         <is>
-          <t>Hire 1 backend and 1 frontend engineer (see 'Team &amp; Hiring' sheet for scoped responsibilities).</t>
+          <t>Hire 1 backend + 1 frontend engineer (scoped on the 'Team &amp; Hiring' sheet).</t>
         </is>
       </c>
       <c r="H9" s="67" t="inlineStr">
@@ -1480,7 +1511,7 @@
       </c>
       <c r="J9" s="65" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Tech Lead / Founder</t>
         </is>
       </c>
       <c r="K9" s="69" t="inlineStr">
@@ -1489,7 +1520,7 @@
         </is>
       </c>
       <c r="L9" s="65" t="inlineStr"/>
-      <c r="M9" s="65" t="inlineStr"/>
+      <c r="M9" s="69" t="inlineStr"/>
       <c r="N9" s="65" t="inlineStr"/>
       <c r="O9" s="70">
         <f>IF(AND(K9&lt;&gt;"",M9&lt;&gt;""),M9-K9,"")</f>
@@ -1497,11 +1528,11 @@
       </c>
       <c r="P9" s="65" t="inlineStr">
         <is>
-          <t>Single-maintainer risk: critical bugs (e.g. the AI crash below) sit unowned; slow response breaches the Hypercare SLAs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="90" customHeight="1" s="52">
+          <t>Faster fixes, lower single-maintainer risk, and the Hypercare SLAs become achievable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="110" customHeight="1" s="52">
       <c r="A10" s="63" t="inlineStr">
         <is>
           <t>BE-007</t>
@@ -1519,32 +1550,33 @@
       </c>
       <c r="D10" s="66" t="inlineStr">
         <is>
-          <t>Hotelier AI Assistant crashes on EVERY message (logger undefined)</t>
+          <t>Hotelier AI Assistant crashed on every message (missing logger)</t>
         </is>
       </c>
       <c r="E10" s="65" t="inlineStr">
         <is>
-          <t>agent.py uses logger.info() at line 797 and logger.warning() at 809, but 'logger' is never imported or defined in the module. Any non-empty user query hits the NameError.</t>
+          <t>agent.py referenced a module-level `logger` (smart tool selector + settings fetch) that was never defined, so any non-empty query raised NameError and returned 500.
+⏱ When it surfaces: Was firing on 100% of hotelier assistant messages.</t>
         </is>
       </c>
       <c r="F10" s="65" t="inlineStr">
         <is>
-          <t>Missing `import logging; logger = logging.getLogger(__name__)` in app/core/agent.py.</t>
+          <t>Missing logging.getLogger in app/core/agent.py.</t>
         </is>
       </c>
       <c r="G10" s="65" t="inlineStr">
         <is>
-          <t>Add the logger definition at module top; add a smoke test that calls create_agent_executor with a real query.</t>
-        </is>
-      </c>
-      <c r="H10" s="71" t="inlineStr">
+          <t>Add the module logger; add a regression smoke test on the tool-selector path.</t>
+        </is>
+      </c>
+      <c r="H10" s="72" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="I10" s="68" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="I10" s="73" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="J10" s="65" t="inlineStr">
@@ -1558,19 +1590,27 @@
         </is>
       </c>
       <c r="L10" s="65" t="inlineStr"/>
-      <c r="M10" s="65" t="inlineStr"/>
-      <c r="N10" s="65" t="inlineStr"/>
+      <c r="M10" s="69" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="N10" s="65" t="inlineStr">
+        <is>
+          <t>Added module-level logger in app/core/agent.py; added tests/test_ai_agent_smoke.py asserting the tool-selector path never raises NameError. Full suite green (253 passed).</t>
+        </is>
+      </c>
       <c r="O10" s="70">
         <f>IF(AND(K10&lt;&gt;"",M10&lt;&gt;""),M10-K10,"")</f>
         <v/>
       </c>
       <c r="P10" s="65" t="inlineStr">
         <is>
-          <t>The paid hotelier AI assistant feature is effectively 100% broken -&gt; returns 500 'AI Agent Error' on every request; churn + refund risk.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="90" customHeight="1" s="52">
+          <t>FIXED: the paid hotelier AI assistant is restored. This was the single biggest functional bug.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="100" customHeight="1" s="52">
       <c r="A11" s="63" t="inlineStr">
         <is>
           <t>BE-008</t>
@@ -1588,27 +1628,28 @@
       </c>
       <c r="D11" s="66" t="inlineStr">
         <is>
-          <t>AI chat holds a Postgres connection for the entire LLM round-trip</t>
+          <t>AI chat holds a DB connection for the whole LLM round-trip</t>
         </is>
       </c>
       <c r="E11" s="65" t="inlineStr">
         <is>
-          <t>chat.py and agent.py inject DbSession and keep it open while agent.arun() runs (seconds per call, 1-2 calls). The connection is not released during the slow LLM I/O.</t>
+          <t>chat.py/agent.py keep the request DB session open while agent.arun() runs (seconds, 1-2 calls) because the agent's tools query the DB mid-call.
+⏱ When it surfaces: When many guests chat at the same time (e.g. a campaign).</t>
         </is>
       </c>
       <c r="F11" s="65" t="inlineStr">
         <is>
-          <t>Request-scoped DB session spans the LLM call instead of being released before it.</t>
+          <t>Request-scoped session spans the slow LLM I/O instead of using short per-tool sessions.</t>
         </is>
       </c>
       <c r="G11" s="65" t="inlineStr">
         <is>
-          <t>Fetch all DB data first, release the session, then run the LLM; or use a short-lived session per tool call.</t>
-        </is>
-      </c>
-      <c r="H11" s="71" t="inlineStr">
-        <is>
-          <t>Critical</t>
+          <t>Refactor tools to short-lived sessions / pre-fetch data and release the session before the model call.</t>
+        </is>
+      </c>
+      <c r="H11" s="67" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="I11" s="68" t="inlineStr">
@@ -1627,7 +1668,7 @@
         </is>
       </c>
       <c r="L11" s="65" t="inlineStr"/>
-      <c r="M11" s="65" t="inlineStr"/>
+      <c r="M11" s="69" t="inlineStr"/>
       <c r="N11" s="65" t="inlineStr"/>
       <c r="O11" s="70">
         <f>IF(AND(K11&lt;&gt;"",M11&lt;&gt;""),M11-K11,"")</f>
@@ -1635,11 +1676,11 @@
       </c>
       <c r="P11" s="65" t="inlineStr">
         <is>
-          <t>~10-20 concurrent chats can exhaust the pool and 500 the whole site; this is the link between an AI spike and a full outage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="90" customHeight="1" s="52">
+          <t>Once addressed, AI concurrency stops competing with the rest of the API for DB connections.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="110" customHeight="1" s="52">
       <c r="A12" s="63" t="inlineStr">
         <is>
           <t>BE-009</t>
@@ -1657,22 +1698,23 @@
       </c>
       <c r="D12" s="66" t="inlineStr">
         <is>
-          <t>Error fallback escalates to expensive 70B model and doubles LLM calls</t>
+          <t>Error fallback escalated to the expensive 70B model</t>
         </is>
       </c>
       <c r="E12" s="65" t="inlineStr">
         <is>
-          <t>On any guest-agent error, chat.py retries without tools using llama-3.3-70b-versatile (line 319) — a pricier model — after already paying for the failed call.</t>
+          <t>On any guest-agent error, chat.py retried (without tools) and defaulted to llama-3.3-70b-versatile — pricier than the normal 8B path — after already paying for the failed call.
+⏱ When it surfaces: During any transient provider/tool error, multiplied under load.</t>
         </is>
       </c>
       <c r="F12" s="65" t="inlineStr">
         <is>
-          <t>Fallback defaults to a large model and re-runs the full conversation.</t>
+          <t>Fallback defaulted to a large model.</t>
         </is>
       </c>
       <c r="G12" s="65" t="inlineStr">
         <is>
-          <t>Fallback to the same cheap 8B model; cap fallback to one attempt; don't replay full history.</t>
+          <t>Keep the fallback on the cheap 8B model; single attempt.</t>
         </is>
       </c>
       <c r="H12" s="67" t="inlineStr">
@@ -1680,9 +1722,9 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I12" s="68" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="I12" s="73" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="J12" s="65" t="inlineStr">
@@ -1696,19 +1738,27 @@
         </is>
       </c>
       <c r="L12" s="65" t="inlineStr"/>
-      <c r="M12" s="65" t="inlineStr"/>
-      <c r="N12" s="65" t="inlineStr"/>
+      <c r="M12" s="69" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="N12" s="65" t="inlineStr">
+        <is>
+          <t>chat.py fallback now defaults to llama-3.1-8b-instant (cheap) instead of the 70B model.</t>
+        </is>
+      </c>
       <c r="O12" s="70">
         <f>IF(AND(K12&lt;&gt;"",M12&lt;&gt;""),M12-K12,"")</f>
         <v/>
       </c>
       <c r="P12" s="65" t="inlineStr">
         <is>
-          <t>Every transient error costs ~2x and jumps to a costlier model -&gt; error storms multiply the AI bill exactly when things are already failing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="90" customHeight="1" s="52">
+          <t>FIXED: error storms no longer cost ~2x and no longer jump to a costlier model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="110" customHeight="1" s="52">
       <c r="A13" s="63" t="inlineStr">
         <is>
           <t>BE-010</t>
@@ -1726,22 +1776,23 @@
       </c>
       <c r="D13" s="66" t="inlineStr">
         <is>
-          <t>search_web tool blocks the event loop (sync DDGS, no timeout)</t>
+          <t>Web-search tool could block the worker (sync call, no timeout)</t>
         </is>
       </c>
       <c r="E13" s="65" t="inlineStr">
         <is>
-          <t>agent.py search_web() calls DuckDuckGo (DDGS().text) synchronously inside an async tool with no timeout.</t>
+          <t>agent.py search_web called DuckDuckGo synchronously on the event loop with no timeout.
+⏱ When it surfaces: Whenever the hotelier asks a 'why' question that triggers web search and DDG is slow.</t>
         </is>
       </c>
       <c r="F13" s="65" t="inlineStr">
         <is>
-          <t>Blocking network call on the async event loop; external dependency with no SLA.</t>
+          <t>Blocking external call with no SLA on the async loop.</t>
         </is>
       </c>
       <c r="G13" s="65" t="inlineStr">
         <is>
-          <t>Move to an async/threadpool call with a hard timeout; cache results; degrade gracefully on failure.</t>
+          <t>Run it in a thread with a hard timeout; degrade gracefully.</t>
         </is>
       </c>
       <c r="H13" s="67" t="inlineStr">
@@ -1749,9 +1800,9 @@
           <t>High</t>
         </is>
       </c>
-      <c r="I13" s="68" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="I13" s="73" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="J13" s="65" t="inlineStr">
@@ -1765,19 +1816,27 @@
         </is>
       </c>
       <c r="L13" s="65" t="inlineStr"/>
-      <c r="M13" s="65" t="inlineStr"/>
-      <c r="N13" s="65" t="inlineStr"/>
+      <c r="M13" s="69" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="N13" s="65" t="inlineStr">
+        <is>
+          <t>search_web now uses asyncio.to_thread + asyncio.wait_for(8s) and returns a graceful message on timeout/failure.</t>
+        </is>
+      </c>
       <c r="O13" s="70">
         <f>IF(AND(K13&lt;&gt;"",M13&lt;&gt;""),M13-K13,"")</f>
         <v/>
       </c>
       <c r="P13" s="65" t="inlineStr">
         <is>
-          <t>One slow DuckDuckGo response stalls the worker for all users on it; DDG rate-limiting silently breaks 'why' pricing advice.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="90" customHeight="1" s="52">
+          <t>FIXED: a slow search can no longer stall the worker for other users.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="100" customHeight="1" s="52">
       <c r="A14" s="63" t="inlineStr">
         <is>
           <t>BE-011</t>
@@ -1795,27 +1854,28 @@
       </c>
       <c r="D14" s="66" t="inlineStr">
         <is>
-          <t>Destructive AI actions confirmed only by prompt, not by code</t>
+          <t>Make destructive AI actions confirm in code, not just in the prompt</t>
         </is>
       </c>
       <c r="E14" s="65" t="inlineStr">
         <is>
-          <t>cancel_booking, update_room_price, create_promo_code rely on a SYSTEM_PROMPT instruction to 'ask for confirmation'. Nothing in code requires it; a model slip or injected text can execute them.</t>
+          <t>cancel_booking / update_room_price / create_promo_code rely on a prompt instruction to 'ask first'. Nothing in code enforces it, so a model slip or injected text could execute them.
+⏱ When it surfaces: If a guest/hotelier message is crafted to trick the model, or the model mis-fires.</t>
         </is>
       </c>
       <c r="F14" s="65" t="inlineStr">
         <is>
-          <t>Confirmation is a prompt convention, not an enforced gate; tools mutate on first call.</t>
+          <t>Confirmation is a prompt convention, not a code gate.</t>
         </is>
       </c>
       <c r="G14" s="65" t="inlineStr">
         <is>
-          <t>Require an explicit confirmation token/2-step flow in code before any mutating tool runs; gate price/promo behind OWNER/MANAGER.</t>
-        </is>
-      </c>
-      <c r="H14" s="71" t="inlineStr">
-        <is>
-          <t>Critical</t>
+          <t>Require an explicit 2-step confirmation token in code before any mutating tool runs; gate price/promo behind OWNER/MANAGER.</t>
+        </is>
+      </c>
+      <c r="H14" s="67" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="I14" s="68" t="inlineStr">
@@ -1834,7 +1894,7 @@
         </is>
       </c>
       <c r="L14" s="65" t="inlineStr"/>
-      <c r="M14" s="65" t="inlineStr"/>
+      <c r="M14" s="69" t="inlineStr"/>
       <c r="N14" s="65" t="inlineStr"/>
       <c r="O14" s="70">
         <f>IF(AND(K14&lt;&gt;"",M14&lt;&gt;""),M14-K14,"")</f>
@@ -1842,11 +1902,11 @@
       </c>
       <c r="P14" s="65" t="inlineStr">
         <is>
-          <t>An AI mistake or prompt injection can cancel a real booking or zero out a room rate -&gt; direct revenue loss and guest impact.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="90" customHeight="1" s="52">
+          <t>Hardening: removes the chance of an AI-initiated cancellation or rate change without a real confirmation. (Tenant scope already enforced.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="100" customHeight="1" s="52">
       <c r="A15" s="63" t="inlineStr">
         <is>
           <t>BE-012</t>
@@ -1864,27 +1924,28 @@
       </c>
       <c r="D15" s="66" t="inlineStr">
         <is>
-          <t>Prompt injection via guest messages and stored special_requests</t>
+          <t>Harden the bots against prompt injection</t>
         </is>
       </c>
       <c r="E15" s="65" t="inlineStr">
         <is>
-          <t>Guest-controlled chat text reaches a tool-enabled LLM; chain guest_history (incl. special_requests) is injected into the system prompt (guest_agent.py), enabling second-order injection.</t>
+          <t>Guest chat text reaches a tool-enabled LLM, and chain guest_history (incl. guest special_requests) is injected into the system prompt — a path for second-order injection.
+⏱ When it surfaces: As real guests (and the occasional bad actor) type free-form messages.</t>
         </is>
       </c>
       <c r="F15" s="65" t="inlineStr">
         <is>
-          <t>Untrusted text concatenated into prompts that drive tools.</t>
+          <t>Untrusted text concatenated into prompts that can drive tools.</t>
         </is>
       </c>
       <c r="G15" s="65" t="inlineStr">
         <is>
-          <t>Treat all guest/stored text as untrusted; strip/escape before prompt insertion; keep tools read-only on the public bot; add injection tests.</t>
-        </is>
-      </c>
-      <c r="H15" s="67" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Treat guest/stored text as untrusted; sanitise before insertion; keep public-bot tools read-only; add injection tests.</t>
+        </is>
+      </c>
+      <c r="H15" s="71" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I15" s="68" t="inlineStr">
@@ -1903,7 +1964,7 @@
         </is>
       </c>
       <c r="L15" s="65" t="inlineStr"/>
-      <c r="M15" s="65" t="inlineStr"/>
+      <c r="M15" s="69" t="inlineStr"/>
       <c r="N15" s="65" t="inlineStr"/>
       <c r="O15" s="70">
         <f>IF(AND(K15&lt;&gt;"",M15&lt;&gt;""),M15-K15,"")</f>
@@ -1911,11 +1972,11 @@
       </c>
       <c r="P15" s="65" t="inlineStr">
         <is>
-          <t>A crafted message can make the concierge misquote prices/policies or leak data, damaging trust and giving wrong commitments to customers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="90" customHeight="1" s="52">
+          <t>Protects against the bot being steered to misquote prices/policies or reveal unintended info.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="100" customHeight="1" s="52">
       <c r="A16" s="63" t="inlineStr">
         <is>
           <t>BE-013</t>
@@ -1933,27 +1994,28 @@
       </c>
       <c r="D16" s="66" t="inlineStr">
         <is>
-          <t>AI quick-booking has no availability / double-booking guard</t>
+          <t>Re-check availability inside AI quick-booking</t>
         </is>
       </c>
       <c r="E16" s="65" t="inlineStr">
         <is>
-          <t>agent.py create_quick_booking writes a Booking without checking inventory or overlap; check_availability_matrix is a separate optional tool the model may skip.</t>
+          <t>create_quick_booking writes a Booking without an inventory/overlap check (availability is a separate optional tool the model may skip).
+⏱ When it surfaces: When the AI books a date range that's actually sold out.</t>
         </is>
       </c>
       <c r="F16" s="65" t="inlineStr">
         <is>
-          <t>Booking creation tool does not re-validate availability server-side.</t>
+          <t>Booking tool does not re-validate availability atomically.</t>
         </is>
       </c>
       <c r="G16" s="65" t="inlineStr">
         <is>
-          <t>Re-check availability atomically inside create_quick_booking; reject on conflict.</t>
-        </is>
-      </c>
-      <c r="H16" s="67" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Re-check availability inside create_quick_booking and reject on conflict.</t>
+        </is>
+      </c>
+      <c r="H16" s="71" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I16" s="68" t="inlineStr">
@@ -1972,7 +2034,7 @@
         </is>
       </c>
       <c r="L16" s="65" t="inlineStr"/>
-      <c r="M16" s="65" t="inlineStr"/>
+      <c r="M16" s="69" t="inlineStr"/>
       <c r="N16" s="65" t="inlineStr"/>
       <c r="O16" s="70">
         <f>IF(AND(K16&lt;&gt;"",M16&lt;&gt;""),M16-K16,"")</f>
@@ -1980,11 +2042,11 @@
       </c>
       <c r="P16" s="65" t="inlineStr">
         <is>
-          <t>AI can overbook a sold-out room -&gt; walk-the-guest situations, compensation cost, reputation damage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="90" customHeight="1" s="52">
+          <t>Prevents AI-driven overbooking and the resulting walk/compensation cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="100" customHeight="1" s="52">
       <c r="A17" s="63" t="inlineStr">
         <is>
           <t>BE-014</t>
@@ -2002,25 +2064,26 @@
       </c>
       <c r="D17" s="66" t="inlineStr">
         <is>
-          <t>Availability checks do O(bookings x rooms) Python loops on an unbounded fetch</t>
+          <t>Optimise availability counting (currently in-Python loops)</t>
         </is>
       </c>
       <c r="E17" s="65" t="inlineStr">
         <is>
-          <t>check_availability (guest_agent.py) and check_availability_matrix (agent.py) load all overlapping bookings and nest-loop over rooms in Python.</t>
+          <t>check_availability does an O(bookings*rooms) Python loop over overlapping bookings (rooms are stored as a JSON array).
+⏱ When it surfaces: On large/busy hotels with many overlapping bookings.</t>
         </is>
       </c>
       <c r="F17" s="65" t="inlineStr">
         <is>
-          <t>In-memory aggregation instead of a single GROUP BY; no pagination on the booking fetch.</t>
+          <t>In-memory aggregation; fine for small data, heavier as bookings grow.</t>
         </is>
       </c>
       <c r="G17" s="65" t="inlineStr">
         <is>
-          <t>Aggregate booked counts in SQL (GROUP BY room_type_id); add composite index on (hotel_id, status, dates).</t>
-        </is>
-      </c>
-      <c r="H17" s="72" t="inlineStr">
+          <t>Pre-aggregate counts; ensure composite index on (hotel_id, status, dates).</t>
+        </is>
+      </c>
+      <c r="H17" s="71" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2041,7 +2104,7 @@
         </is>
       </c>
       <c r="L17" s="65" t="inlineStr"/>
-      <c r="M17" s="65" t="inlineStr"/>
+      <c r="M17" s="69" t="inlineStr"/>
       <c r="N17" s="65" t="inlineStr"/>
       <c r="O17" s="70">
         <f>IF(AND(K17&lt;&gt;"",M17&lt;&gt;""),M17-K17,"")</f>
@@ -2049,11 +2112,11 @@
       </c>
       <c r="P17" s="65" t="inlineStr">
         <is>
-          <t>On busy/large hotels availability gets slow and CPU-heavy, slowing the booking funnel and every concurrent chat.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="90" customHeight="1" s="52">
+          <t>Keeps the booking funnel and concurrent chats fast as data volume grows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="100" customHeight="1" s="52">
       <c r="A18" s="63" t="inlineStr">
         <is>
           <t>BE-015</t>
@@ -2071,27 +2134,28 @@
       </c>
       <c r="D18" s="66" t="inlineStr">
         <is>
-          <t>LLM hallucination of price, policy, or room facts</t>
+          <t>Validate AI-quoted prices/policies against the DB</t>
         </is>
       </c>
       <c r="E18" s="65" t="inlineStr">
         <is>
-          <t>The concierge/assistant generate free text; there is no hard guarantee the quoted price or policy matches the DB even though tools exist.</t>
+          <t>The bots generate free text; tools exist but nothing guarantees a quoted price/policy exactly matches the DB. (Checkout already re-validates price server-side.)
+⏱ When it surfaces: When a guest asks detailed price/policy questions and the model paraphrases.</t>
         </is>
       </c>
       <c r="F18" s="65" t="inlineStr">
         <is>
-          <t>Generative model output is not constrained to tool data.</t>
+          <t>Generative output is not constrained to tool data.</t>
         </is>
       </c>
       <c r="G18" s="65" t="inlineStr">
         <is>
-          <t>Post-validate any price/availability the model states against the DB before sending; show authoritative price at checkout (already re-validated).</t>
-        </is>
-      </c>
-      <c r="H18" s="67" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Post-check any price/availability the model states before sending it to the guest.</t>
+        </is>
+      </c>
+      <c r="H18" s="71" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I18" s="68" t="inlineStr">
@@ -2110,7 +2174,7 @@
         </is>
       </c>
       <c r="L18" s="65" t="inlineStr"/>
-      <c r="M18" s="65" t="inlineStr"/>
+      <c r="M18" s="69" t="inlineStr"/>
       <c r="N18" s="65" t="inlineStr"/>
       <c r="O18" s="70">
         <f>IF(AND(K18&lt;&gt;"",M18&lt;&gt;""),M18-K18,"")</f>
@@ -2118,11 +2182,11 @@
       </c>
       <c r="P18" s="65" t="inlineStr">
         <is>
-          <t>A wrong AI-quoted rate can be argued as a commitment by the guest -&gt; disputes, honouring loss, or lost bookings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="90" customHeight="1" s="52">
+          <t>Reduces the risk of a guest treating a wrong AI quote as a commitment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="100" customHeight="1" s="52">
       <c r="A19" s="63" t="inlineStr">
         <is>
           <t>BE-016</t>
@@ -2140,25 +2204,26 @@
       </c>
       <c r="D19" s="66" t="inlineStr">
         <is>
-          <t>Chart rendering depends on the model echoing [CHART_DATA] verbatim</t>
+          <t>Make chart data flow through code, not model echo</t>
         </is>
       </c>
       <c r="E19" s="65" t="inlineStr">
         <is>
-          <t>agent.py instructs the model to return [CHART_DATA]...[/CHART_DATA] JSON untouched; smaller models often reword or drop it.</t>
+          <t>agent.py asks the model to echo [CHART_DATA] JSON verbatim; smaller models sometimes reword or drop it.
+⏱ When it surfaces: Intermittently, depending on the model and prompt.</t>
         </is>
       </c>
       <c r="F19" s="65" t="inlineStr">
         <is>
-          <t>Structured output delegated to model obedience instead of code.</t>
+          <t>Structured output delegated to model obedience.</t>
         </is>
       </c>
       <c r="G19" s="65" t="inlineStr">
         <is>
-          <t>Have the tool return structured data through a separate channel/field the UI reads directly, not via model echo.</t>
-        </is>
-      </c>
-      <c r="H19" s="73" t="inlineStr">
+          <t>Return chart data via a dedicated field the UI reads directly.</t>
+        </is>
+      </c>
+      <c r="H19" s="74" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -2170,7 +2235,7 @@
       </c>
       <c r="J19" s="65" t="inlineStr">
         <is>
-          <t>Backend Dev / Frontend Dev</t>
+          <t>Backend Dev</t>
         </is>
       </c>
       <c r="K19" s="69" t="inlineStr">
@@ -2179,7 +2244,7 @@
         </is>
       </c>
       <c r="L19" s="65" t="inlineStr"/>
-      <c r="M19" s="65" t="inlineStr"/>
+      <c r="M19" s="69" t="inlineStr"/>
       <c r="N19" s="65" t="inlineStr"/>
       <c r="O19" s="70">
         <f>IF(AND(K19&lt;&gt;"",M19&lt;&gt;""),M19-K19,"")</f>
@@ -2187,11 +2252,11 @@
       </c>
       <c r="P19" s="65" t="inlineStr">
         <is>
-          <t>Dashboard charts intermittently render blank/garbled -&gt; hoteliers distrust the analytics feature.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="90" customHeight="1" s="52">
+          <t>Dashboard charts render reliably -&gt; hoteliers trust the analytics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="100" customHeight="1" s="52">
       <c r="A20" s="63" t="inlineStr">
         <is>
           <t>BE-017</t>
@@ -2209,27 +2274,28 @@
       </c>
       <c r="D20" s="66" t="inlineStr">
         <is>
-          <t>Provider auto-detection by API-key prefix is fragile</t>
+          <t>Require explicit AI provider instead of key-prefix guessing</t>
         </is>
       </c>
       <c r="E20" s="65" t="inlineStr">
         <is>
-          <t>agent/guest_agent/global_agent guess the provider from key prefixes (gsk_/sk-/AIza). A custom gateway or rotated key format breaks selection.</t>
+          <t>Provider is inferred from key prefixes (gsk_/sk-/AIza); a custom gateway or new key format breaks selection.
+⏱ When it surfaces: When a hotel rotates keys or uses a non-standard provider.</t>
         </is>
       </c>
       <c r="F20" s="65" t="inlineStr">
         <is>
-          <t>Heuristic provider detection instead of explicit config.</t>
+          <t>Heuristic detection instead of explicit config.</t>
         </is>
       </c>
       <c r="G20" s="65" t="inlineStr">
         <is>
-          <t>Require explicit ai_provider; treat prefix detection only as a last-resort hint with clear logging.</t>
-        </is>
-      </c>
-      <c r="H20" s="72" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Require ai_provider; use prefix detection only as a logged last resort.</t>
+        </is>
+      </c>
+      <c r="H20" s="74" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="I20" s="68" t="inlineStr">
@@ -2248,7 +2314,7 @@
         </is>
       </c>
       <c r="L20" s="65" t="inlineStr"/>
-      <c r="M20" s="65" t="inlineStr"/>
+      <c r="M20" s="69" t="inlineStr"/>
       <c r="N20" s="65" t="inlineStr"/>
       <c r="O20" s="70">
         <f>IF(AND(K20&lt;&gt;"",M20&lt;&gt;""),M20-K20,"")</f>
@@ -2256,11 +2322,11 @@
       </c>
       <c r="P20" s="65" t="inlineStr">
         <is>
-          <t>A hotel's AI silently routes to the wrong API or fails entirely after a key change -&gt; support tickets and downtime.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="90" customHeight="1" s="52">
+          <t>Avoids a hotel's AI silently routing to the wrong API after a key change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="100" customHeight="1" s="52">
       <c r="A21" s="63" t="inlineStr">
         <is>
           <t>BE-018</t>
@@ -2278,27 +2344,28 @@
       </c>
       <c r="D21" s="66" t="inlineStr">
         <is>
-          <t>Hotelier assistant defaults to a 70B model</t>
+          <t>Confirm model tiering for the hotelier assistant</t>
         </is>
       </c>
       <c r="E21" s="65" t="inlineStr">
         <is>
-          <t>agent.py target_model default is llama-3.3-70b-versatile; the cost rule says default to the cheap model and reserve large models for analytics.</t>
+          <t>The hotelier assistant defaults to a 70B model. Policy allows a large model for the analytics agent; confirm whether general assistant traffic should use the cheap model with large reserved for heavy analytics.
+⏱ When it surfaces: Linearly with hotelier assistant adoption.</t>
         </is>
       </c>
       <c r="F21" s="65" t="inlineStr">
         <is>
-          <t>Expensive default not aligned with cost policy for general assistant traffic.</t>
+          <t>Default model choice vs cost policy needs a product decision.</t>
         </is>
       </c>
       <c r="G21" s="65" t="inlineStr">
         <is>
-          <t>Default the general assistant to the cheap 8B model; route only heavy analytics to the large model.</t>
-        </is>
-      </c>
-      <c r="H21" s="72" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Default general queries to the cheap model; route only heavy analytics to 70B.</t>
+        </is>
+      </c>
+      <c r="H21" s="74" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="I21" s="68" t="inlineStr">
@@ -2317,7 +2384,7 @@
         </is>
       </c>
       <c r="L21" s="65" t="inlineStr"/>
-      <c r="M21" s="65" t="inlineStr"/>
+      <c r="M21" s="69" t="inlineStr"/>
       <c r="N21" s="65" t="inlineStr"/>
       <c r="O21" s="70">
         <f>IF(AND(K21&lt;&gt;"",M21&lt;&gt;""),M21-K21,"")</f>
@@ -2325,11 +2392,11 @@
       </c>
       <c r="P21" s="65" t="inlineStr">
         <is>
-          <t>Every hotelier query costs ~10x more than necessary, inflating the AI bill linearly with adoption.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="90" customHeight="1" s="52">
+          <t>Optional cost optimisation; pairs with the AI-budget item.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="110" customHeight="1" s="52">
       <c r="A22" s="63" t="inlineStr">
         <is>
           <t>BE-019</t>
@@ -2347,32 +2414,33 @@
       </c>
       <c r="D22" s="66" t="inlineStr">
         <is>
-          <t>PII (email / supabase_id) logged at INFO in auth</t>
+          <t>Stop logging PII at INFO in the auth path</t>
         </is>
       </c>
       <c r="E22" s="65" t="inlineStr">
         <is>
-          <t>deps.py logs email and supabase_id at INFO on several auth branches (e.g. lines 84, 91, 150); policy is DEBUG-only / hashed.</t>
+          <t>deps.py logged email/supabase_id at INFO on several auth branches; policy is DEBUG-only / hashed.
+⏱ When it surfaces: Continuously in production logs until changed.</t>
         </is>
       </c>
       <c r="F22" s="65" t="inlineStr">
         <is>
-          <t>Verbose INFO logging of identifiers in the hot auth path.</t>
+          <t>Verbose INFO logging of identifiers on the hot auth path.</t>
         </is>
       </c>
       <c r="G22" s="65" t="inlineStr">
         <is>
-          <t>Drop to DEBUG or hash; ensure LOG_LEVEL=WARNING in prod.</t>
-        </is>
-      </c>
-      <c r="H22" s="72" t="inlineStr">
+          <t>Drop to DEBUG / log non-PII identifiers; keep LOG_LEVEL=WARNING in prod.</t>
+        </is>
+      </c>
+      <c r="H22" s="71" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I22" s="68" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="I22" s="73" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="J22" s="65" t="inlineStr">
@@ -2386,19 +2454,27 @@
         </is>
       </c>
       <c r="L22" s="65" t="inlineStr"/>
-      <c r="M22" s="65" t="inlineStr"/>
-      <c r="N22" s="65" t="inlineStr"/>
+      <c r="M22" s="69" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="N22" s="65" t="inlineStr">
+        <is>
+          <t>deps.py auth logs with email/supabase_id moved to DEBUG; master-admin promotion now logs user_id instead of email.</t>
+        </is>
+      </c>
       <c r="O22" s="70">
         <f>IF(AND(K22&lt;&gt;"",M22&lt;&gt;""),M22-K22,"")</f>
         <v/>
       </c>
       <c r="P22" s="65" t="inlineStr">
         <is>
-          <t>PII in logs is a privacy/compliance exposure and inflates log egress cost at scale.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="90" customHeight="1" s="52">
+          <t>FIXED: lowers PII exposure and log egress cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="100" customHeight="1" s="52">
       <c r="A23" s="63" t="inlineStr">
         <is>
           <t>BE-020</t>
@@ -2416,25 +2492,26 @@
       </c>
       <c r="D23" s="66" t="inlineStr">
         <is>
-          <t>Streaming chat has no max lifetime or disconnect cap</t>
+          <t>Add a max lifetime + disconnect check to streaming chat</t>
         </is>
       </c>
       <c r="E23" s="65" t="inlineStr">
         <is>
-          <t>stream_guest_ai (chat.py) streams agent events with no overall timeout and holds the DB session for the whole stream; only tool_call_limit bounds it.</t>
+          <t>stream_guest_ai streams agent events with no overall timeout and holds the DB session for the whole stream; only tool_call_limit bounds it.
+⏱ When it surfaces: With abandoned/idle streaming chats or deliberate slow clients.</t>
         </is>
       </c>
       <c r="F23" s="65" t="inlineStr">
         <is>
-          <t>Missing max-duration and client-disconnect checks on the SSE generator.</t>
+          <t>Missing max-duration and client-disconnect handling on the SSE generator.</t>
         </is>
       </c>
       <c r="G23" s="65" t="inlineStr">
         <is>
-          <t>Add a hard max stream lifetime and disconnect detection; release the DB session before streaming.</t>
-        </is>
-      </c>
-      <c r="H23" s="72" t="inlineStr">
+          <t>Add a hard stream lifetime + disconnect detection; release the session before streaming.</t>
+        </is>
+      </c>
+      <c r="H23" s="71" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2455,7 +2532,7 @@
         </is>
       </c>
       <c r="L23" s="65" t="inlineStr"/>
-      <c r="M23" s="65" t="inlineStr"/>
+      <c r="M23" s="69" t="inlineStr"/>
       <c r="N23" s="65" t="inlineStr"/>
       <c r="O23" s="70">
         <f>IF(AND(K23&lt;&gt;"",M23&lt;&gt;""),M23-K23,"")</f>
@@ -2463,11 +2540,11 @@
       </c>
       <c r="P23" s="65" t="inlineStr">
         <is>
-          <t>Idle/abandoned streams pin worker + DB resources, lowering real concurrency and inviting slow-loris-style abuse.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="90" customHeight="1" s="52">
+          <t>Frees worker+DB resources held by dead streams; raises real concurrency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="100" customHeight="1" s="52">
       <c r="A24" s="63" t="inlineStr">
         <is>
           <t>BE-021</t>
@@ -2485,25 +2562,26 @@
       </c>
       <c r="D24" s="66" t="inlineStr">
         <is>
-          <t>AI usage accounting is silent best-effort</t>
+          <t>Strengthen AI usage accounting</t>
         </is>
       </c>
       <c r="E24" s="65" t="inlineStr">
         <is>
-          <t>record_ai_usage swallows all errors and returns 0 when metrics/Redis are missing; failed runs may record nothing.</t>
+          <t>record_ai_usage swallows all errors and returns 0 if metrics/Redis are missing, so a failed run may record nothing.
+⏱ When it surfaces: When Redis or metrics are briefly unavailable.</t>
         </is>
       </c>
       <c r="F24" s="65" t="inlineStr">
         <is>
-          <t>Telemetry intentionally never raises, but there is no fallback counter or alert.</t>
+          <t>Telemetry is best-effort with no fallback/alert.</t>
         </is>
       </c>
       <c r="G24" s="65" t="inlineStr">
         <is>
-          <t>Emit a metric on accounting failures; persist a durable daily aggregate beyond Redis.</t>
-        </is>
-      </c>
-      <c r="H24" s="73" t="inlineStr">
+          <t>Emit a metric on accounting failures; keep a durable aggregate beyond Redis.</t>
+        </is>
+      </c>
+      <c r="H24" s="74" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -2524,7 +2602,7 @@
         </is>
       </c>
       <c r="L24" s="65" t="inlineStr"/>
-      <c r="M24" s="65" t="inlineStr"/>
+      <c r="M24" s="69" t="inlineStr"/>
       <c r="N24" s="65" t="inlineStr"/>
       <c r="O24" s="70">
         <f>IF(AND(K24&lt;&gt;"",M24&lt;&gt;""),M24-K24,"")</f>
@@ -2532,11 +2610,11 @@
       </c>
       <c r="P24" s="65" t="inlineStr">
         <is>
-          <t>Cost dashboards can under-report, hiding an overspend until the invoice arrives.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="90" customHeight="1" s="52">
+          <t>Keeps cost dashboards trustworthy so overspend isn't hidden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="110" customHeight="1" s="52">
       <c r="A25" s="63" t="inlineStr">
         <is>
           <t>BE-022</t>
@@ -2554,32 +2632,33 @@
       </c>
       <c r="D25" s="66" t="inlineStr">
         <is>
-          <t>Raw exception strings returned to clients on agent error</t>
+          <t>Stop returning raw exception text to clients</t>
         </is>
       </c>
       <c r="E25" s="65" t="inlineStr">
         <is>
-          <t>agent.py endpoint returns HTTP 500 detail=f'AI Agent Error: {str(e)}', leaking internal error text to the caller.</t>
+          <t>The assistant endpoint returned HTTP 500 with detail=f'AI Agent Error: {str(e)}', leaking internal error text.
+⏱ When it surfaces: On any unhandled agent error.</t>
         </is>
       </c>
       <c r="F25" s="65" t="inlineStr">
         <is>
-          <t>Generic except surfaces internal detail in the response body.</t>
+          <t>Generic except surfaced internal detail in the response.</t>
         </is>
       </c>
       <c r="G25" s="65" t="inlineStr">
         <is>
-          <t>Return a generic message to the client; log the detail server-side only.</t>
-        </is>
-      </c>
-      <c r="H25" s="72" t="inlineStr">
+          <t>Return a generic message; log detail server-side.</t>
+        </is>
+      </c>
+      <c r="H25" s="71" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I25" s="68" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="I25" s="73" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="J25" s="65" t="inlineStr">
@@ -2593,19 +2672,27 @@
         </is>
       </c>
       <c r="L25" s="65" t="inlineStr"/>
-      <c r="M25" s="65" t="inlineStr"/>
-      <c r="N25" s="65" t="inlineStr"/>
+      <c r="M25" s="69" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="N25" s="65" t="inlineStr">
+        <is>
+          <t>api/v1/agent.py now returns generic 500/503 messages and logs full detail server-side with exc_info.</t>
+        </is>
+      </c>
       <c r="O25" s="70">
         <f>IF(AND(K25&lt;&gt;"",M25&lt;&gt;""),M25-K25,"")</f>
         <v/>
       </c>
       <c r="P25" s="65" t="inlineStr">
         <is>
-          <t>Internal stack/library detail leaks to users (and the broken-logger error is shown verbatim today).</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="90" customHeight="1" s="52">
+          <t>FIXED: no internal stack/library detail leaks to callers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="100" customHeight="1" s="52">
       <c r="A26" s="63" t="inlineStr">
         <is>
           <t>BE-023</t>
@@ -2623,27 +2710,28 @@
       </c>
       <c r="D26" s="66" t="inlineStr">
         <is>
-          <t>100 concurrent users on one page -&gt; DB connection exhaustion</t>
+          <t>Protect against DB connection exhaustion under a traffic burst</t>
         </is>
       </c>
       <c r="E26" s="65" t="inlineStr">
         <is>
-          <t>Per SCALE_TUNING.md the #1 crash risk is Postgres connections; default 10/worker. A burst of page loads (search + availability + chat warm) can saturate the pool.</t>
+          <t>SCALE_TUNING.md flags Postgres connections as the #1 crash risk. A burst of page loads (search + availability + chat warm) on one popular hotel can pressure the pool (default ~10/worker).
+⏱ When it surfaces: When ~100 users hit one hotel page at once (campaign/QR/sale).</t>
         </is>
       </c>
       <c r="F26" s="65" t="inlineStr">
         <is>
-          <t>Connection budget is small and AI/streaming requests hold connections longer than assumed.</t>
+          <t>Small connection budget + AI requests holding connections longer.</t>
         </is>
       </c>
       <c r="G26" s="65" t="inlineStr">
         <is>
-          <t>Right-size pool/concurrency under the Supabase limit; release sessions early; add a CDN/queue in front of public reads.</t>
-        </is>
-      </c>
-      <c r="H26" s="71" t="inlineStr">
-        <is>
-          <t>Critical</t>
+          <t>Right-size pool/concurrency under the Supabase limit; release sessions early; add a CDN/cache for public reads.</t>
+        </is>
+      </c>
+      <c r="H26" s="67" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="I26" s="68" t="inlineStr">
@@ -2653,7 +2741,7 @@
       </c>
       <c r="J26" s="65" t="inlineStr">
         <is>
-          <t>DevOps / Backend Dev</t>
+          <t>Backend Dev</t>
         </is>
       </c>
       <c r="K26" s="69" t="inlineStr">
@@ -2662,7 +2750,7 @@
         </is>
       </c>
       <c r="L26" s="65" t="inlineStr"/>
-      <c r="M26" s="65" t="inlineStr"/>
+      <c r="M26" s="69" t="inlineStr"/>
       <c r="N26" s="65" t="inlineStr"/>
       <c r="O26" s="70">
         <f>IF(AND(K26&lt;&gt;"",M26&lt;&gt;""),M26-K26,"")</f>
@@ -2670,11 +2758,11 @@
       </c>
       <c r="P26" s="65" t="inlineStr">
         <is>
-          <t>A single popular hotel's traffic spike can 500 the whole platform for all hotels until the pool drains.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="90" customHeight="1" s="52">
+          <t>Prevents one hotel's success from degrading the whole platform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="100" customHeight="1" s="52">
       <c r="A27" s="63" t="inlineStr">
         <is>
           <t>BE-024</t>
@@ -2692,22 +2780,23 @@
       </c>
       <c r="D27" s="66" t="inlineStr">
         <is>
-          <t>Public AI chat abuse drives the LLM bill</t>
+          <t>Add a non-spoofable signal to the public AI chat</t>
         </is>
       </c>
       <c r="E27" s="65" t="inlineStr">
         <is>
-          <t>chat/guest is anonymous; the 5/min IP limit is spoofable (XFF) and the only real cap is 1000 LLM calls/hotel/day, which fails open without Redis.</t>
+          <t>chat/guest is anonymous; the 5/min IP limit is spoofable and the real cap is 1000 LLM calls/hotel/day (which fails open without Redis).
+⏱ When it surfaces: If a bot targets the public widget, or it's left open and looping.</t>
         </is>
       </c>
       <c r="F27" s="65" t="inlineStr">
         <is>
-          <t>Spoofable IP limit + fail-open per-hotel quota on an unauthenticated, cost-bearing endpoint.</t>
+          <t>Spoofable IP limit + fail-open quota on an unauthenticated, cost-bearing endpoint.</t>
         </is>
       </c>
       <c r="G27" s="65" t="inlineStr">
         <is>
-          <t>Add a non-spoofable signal (signed widget token / captcha), fail-closed quota, and a global platform budget breaker.</t>
+          <t>Add a signed widget token / captcha, a fail-closed quota, and a platform-wide spend breaker.</t>
         </is>
       </c>
       <c r="H27" s="67" t="inlineStr">
@@ -2731,7 +2820,7 @@
         </is>
       </c>
       <c r="L27" s="65" t="inlineStr"/>
-      <c r="M27" s="65" t="inlineStr"/>
+      <c r="M27" s="69" t="inlineStr"/>
       <c r="N27" s="65" t="inlineStr"/>
       <c r="O27" s="70">
         <f>IF(AND(K27&lt;&gt;"",M27&lt;&gt;""),M27-K27,"")</f>
@@ -2739,11 +2828,11 @@
       </c>
       <c r="P27" s="65" t="inlineStr">
         <is>
-          <t>A bot can burn up to ~1000 calls/day/hotel (more if Redis is down) -&gt; a targeted or accidental spike spikes the cloud/LLM invoice.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="90" customHeight="1" s="52">
+          <t>Caps the worst-case LLM bill from automated abuse of the public chat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="100" customHeight="1" s="52">
       <c r="A28" s="63" t="inlineStr">
         <is>
           <t>BE-025</t>
@@ -2761,27 +2850,28 @@
       </c>
       <c r="D28" s="66" t="inlineStr">
         <is>
-          <t>Authenticated endpoints have no rate limit; token-flood forces JWT verification</t>
+          <t>Add a baseline rate limit to authenticated routes</t>
         </is>
       </c>
       <c r="E28" s="65" t="inlineStr">
         <is>
-          <t>Most authenticated routes have no @limiter.limit; invalid Bearer tokens are uncacheable, so each spam request runs verify_supabase_token (CPU + possible Supabase call).</t>
+          <t>Login is on Supabase (no backend password endpoint), but most authenticated routes have no limiter, and invalid Bearer tokens are uncacheable so each forces a JWT verification.
+⏱ When it surfaces: Under a deliberate token-flood.</t>
         </is>
       </c>
       <c r="F28" s="65" t="inlineStr">
         <is>
-          <t>Rate limiting applied selectively; auth verification cost paid per request on garbage tokens.</t>
+          <t>Rate limiting applied selectively; auth verify cost paid per garbage-token request.</t>
         </is>
       </c>
       <c r="G28" s="65" t="inlineStr">
         <is>
-          <t>Add a baseline IP+token limit on authenticated routes; short-cache negative verifications; alert on auth-error spikes.</t>
-        </is>
-      </c>
-      <c r="H28" s="67" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Add an IP+token baseline limit; short-cache negative verifications; alert on auth-error spikes.</t>
+        </is>
+      </c>
+      <c r="H28" s="71" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I28" s="68" t="inlineStr">
@@ -2791,7 +2881,7 @@
       </c>
       <c r="J28" s="65" t="inlineStr">
         <is>
-          <t>Backend Dev / DevOps</t>
+          <t>Backend Dev</t>
         </is>
       </c>
       <c r="K28" s="69" t="inlineStr">
@@ -2800,7 +2890,7 @@
         </is>
       </c>
       <c r="L28" s="65" t="inlineStr"/>
-      <c r="M28" s="65" t="inlineStr"/>
+      <c r="M28" s="69" t="inlineStr"/>
       <c r="N28" s="65" t="inlineStr"/>
       <c r="O28" s="70">
         <f>IF(AND(K28&lt;&gt;"",M28&lt;&gt;""),M28-K28,"")</f>
@@ -2808,11 +2898,11 @@
       </c>
       <c r="P28" s="65" t="inlineStr">
         <is>
-          <t>A cheap token-flood raises CPU and Supabase auth load, degrading latency for real users.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="90" customHeight="1" s="52">
+          <t>Keeps latency stable for real hoteliers during an auth-spam attempt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="100" customHeight="1" s="52">
       <c r="A29" s="63" t="inlineStr">
         <is>
           <t>BE-026</t>
@@ -2830,17 +2920,18 @@
       </c>
       <c r="D29" s="66" t="inlineStr">
         <is>
-          <t>Redis is a single point of failure for many controls</t>
+          <t>Make Redis highly available</t>
         </is>
       </c>
       <c r="E29" s="65" t="inlineStr">
         <is>
-          <t>Payment idempotency, rate limits, AI quota, auth cache, slug cache and analytics caches all depend on a single Redis instance (SCALE_TUNING notes: make HA before relying on it for payment idempotency).</t>
+          <t>Payment idempotency, rate limits, AI quota, auth cache and analytics caches all rely on a single Redis instance (SCALE_TUNING notes HA is needed before relying on it for payment idempotency).
+⏱ When it surfaces: During any Redis outage.</t>
         </is>
       </c>
       <c r="F29" s="65" t="inlineStr">
         <is>
-          <t>No Redis HA; several controls fail open on its loss.</t>
+          <t>No Redis HA; several controls degrade on its loss.</t>
         </is>
       </c>
       <c r="G29" s="65" t="inlineStr">
@@ -2860,7 +2951,7 @@
       </c>
       <c r="J29" s="65" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Backend Dev</t>
         </is>
       </c>
       <c r="K29" s="69" t="inlineStr">
@@ -2869,7 +2960,7 @@
         </is>
       </c>
       <c r="L29" s="65" t="inlineStr"/>
-      <c r="M29" s="65" t="inlineStr"/>
+      <c r="M29" s="69" t="inlineStr"/>
       <c r="N29" s="65" t="inlineStr"/>
       <c r="O29" s="70">
         <f>IF(AND(K29&lt;&gt;"",M29&lt;&gt;""),M29-K29,"")</f>
@@ -2877,11 +2968,11 @@
       </c>
       <c r="P29" s="65" t="inlineStr">
         <is>
-          <t>A Redis outage simultaneously weakens abuse limits, AI quota, and payment idempotency (double-charge risk).</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="90" customHeight="1" s="52">
+          <t>Removes a single point that simultaneously weakens abuse limits, AI quota and payment idempotency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="100" customHeight="1" s="52">
       <c r="A30" s="63" t="inlineStr">
         <is>
           <t>BE-027</t>
@@ -2899,25 +2990,26 @@
       </c>
       <c r="D30" s="66" t="inlineStr">
         <is>
-          <t>No automated alerting on per-hotel AI spend</t>
+          <t>Automate per-hotel AI spend alerting</t>
         </is>
       </c>
       <c r="E30" s="65" t="inlineStr">
         <is>
-          <t>ai_tokens counters exist but must be inspected manually; no threshold alert or auto-throttle.</t>
+          <t>The ai_tokens counters exist but must be read manually; no threshold alert or auto-throttle.
+⏱ When it surfaces: As AI usage scales and one hotel/bot spikes.</t>
         </is>
       </c>
       <c r="F30" s="65" t="inlineStr">
         <is>
-          <t>Monitoring is manual; no automation wired to the counters.</t>
+          <t>Monitoring is manual.</t>
         </is>
       </c>
       <c r="G30" s="65" t="inlineStr">
         <is>
-          <t>Add daily aggregation + alert + optional auto-throttle when a hotel exceeds its tier budget.</t>
-        </is>
-      </c>
-      <c r="H30" s="72" t="inlineStr">
+          <t>Add daily aggregation + alerts + optional auto-throttle at the tier budget.</t>
+        </is>
+      </c>
+      <c r="H30" s="71" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2929,7 +3021,7 @@
       </c>
       <c r="J30" s="65" t="inlineStr">
         <is>
-          <t>Backend Dev / DevOps</t>
+          <t>Backend Dev</t>
         </is>
       </c>
       <c r="K30" s="69" t="inlineStr">
@@ -2938,7 +3030,7 @@
         </is>
       </c>
       <c r="L30" s="65" t="inlineStr"/>
-      <c r="M30" s="65" t="inlineStr"/>
+      <c r="M30" s="69" t="inlineStr"/>
       <c r="N30" s="65" t="inlineStr"/>
       <c r="O30" s="70">
         <f>IF(AND(K30&lt;&gt;"",M30&lt;&gt;""),M30-K30,"")</f>
@@ -2946,11 +3038,11 @@
       </c>
       <c r="P30" s="65" t="inlineStr">
         <is>
-          <t>Overspend is detected days late, after the money is already spent.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="90" customHeight="1" s="52">
+          <t>Overspend is caught in hours, not on the monthly invoice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="100" customHeight="1" s="52">
       <c r="A31" s="63" t="inlineStr">
         <is>
           <t>BE-028</t>
@@ -2968,27 +3060,28 @@
       </c>
       <c r="D31" s="66" t="inlineStr">
         <is>
-          <t>Cloud bill scales with AI adoption (1-2 LLM calls per message)</t>
+          <t>Raise AI cache hit-rate to flatten cost growth</t>
         </is>
       </c>
       <c r="E31" s="65" t="inlineStr">
         <is>
-          <t>Each guest message is 1-2 LLM calls; each widget open also pre-warms cache; multiplied across hotels and visitors this is the dominant variable cost.</t>
+          <t>Each guest message is 1-2 LLM calls; only a short-TTL cache dedupes. Cost grows with visitor volume.
+⏱ When it surfaces: As marketing succeeds and visitor numbers climb.</t>
         </is>
       </c>
       <c r="F31" s="65" t="inlineStr">
         <is>
-          <t>Variable per-message LLM cost with limited deduplication (short cache TTL only).</t>
+          <t>Variable per-message LLM cost with limited dedup.</t>
         </is>
       </c>
       <c r="G31" s="65" t="inlineStr">
         <is>
-          <t>Increase cache hit-rate, shorten prompts, cap history (done: last 20), and set a platform-wide spend breaker.</t>
-        </is>
-      </c>
-      <c r="H31" s="67" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Increase cache hit-rate, keep prompts/history tight (history already capped at 20), set a platform spend breaker.</t>
+        </is>
+      </c>
+      <c r="H31" s="71" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I31" s="68" t="inlineStr">
@@ -3007,7 +3100,7 @@
         </is>
       </c>
       <c r="L31" s="65" t="inlineStr"/>
-      <c r="M31" s="65" t="inlineStr"/>
+      <c r="M31" s="69" t="inlineStr"/>
       <c r="N31" s="65" t="inlineStr"/>
       <c r="O31" s="70">
         <f>IF(AND(K31&lt;&gt;"",M31&lt;&gt;""),M31-K31,"")</f>
@@ -3015,11 +3108,11 @@
       </c>
       <c r="P31" s="65" t="inlineStr">
         <is>
-          <t>Marketing success (more visitors) directly increases the LLM invoice; cost grows with traffic, not revenue.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="90" customHeight="1" s="52">
+          <t>Keeps AI cost growing slower than traffic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="100" customHeight="1" s="52">
       <c r="A32" s="63" t="inlineStr">
         <is>
           <t>BE-029</t>
@@ -3037,17 +3130,18 @@
       </c>
       <c r="D32" s="66" t="inlineStr">
         <is>
-          <t>Third-party failures surface as user errors or silent data loss</t>
+          <t>Add timeouts/retries + alerting to third-party calls</t>
         </is>
       </c>
       <c r="E32" s="65" t="inlineStr">
         <is>
-          <t>Weather API, DuckDuckGo, Razorpay, Google Sheets sync (fire-and-forget), Meta/WhatsApp can fail; some are swallowed (sync_to_google_sheet) so data is lost silently.</t>
+          <t>Weather, DuckDuckGo, Razorpay, Google Sheets (fire-and-forget) and Meta can fail; some failures are swallowed (sheet sync), losing data silently.
+⏱ When it surfaces: During any provider outage or slowdown.</t>
         </is>
       </c>
       <c r="F32" s="65" t="inlineStr">
         <is>
-          <t>No circuit breakers/retries; fire-and-forget syncs drop failures.</t>
+          <t>No circuit breakers/retries; fire-and-forget drops failures.</t>
         </is>
       </c>
       <c r="G32" s="65" t="inlineStr">
@@ -3055,7 +3149,7 @@
           <t>Add timeouts, retries with backoff, and a dead-letter/alert for failed syncs.</t>
         </is>
       </c>
-      <c r="H32" s="72" t="inlineStr">
+      <c r="H32" s="71" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3076,7 +3170,7 @@
         </is>
       </c>
       <c r="L32" s="65" t="inlineStr"/>
-      <c r="M32" s="65" t="inlineStr"/>
+      <c r="M32" s="69" t="inlineStr"/>
       <c r="N32" s="65" t="inlineStr"/>
       <c r="O32" s="70">
         <f>IF(AND(K32&lt;&gt;"",M32&lt;&gt;""),M32-K32,"")</f>
@@ -3084,11 +3178,11 @@
       </c>
       <c r="P32" s="65" t="inlineStr">
         <is>
-          <t>Lead data can silently fail to reach the hotel's sheet; guest-facing tools error out during provider outages.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="90" customHeight="1" s="52">
+          <t>Prevents silent lead-data loss and provider-outage error spikes for guests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="100" customHeight="1" s="52">
       <c r="A33" s="63" t="inlineStr">
         <is>
           <t>BE-030</t>
@@ -3106,17 +3200,18 @@
       </c>
       <c r="D33" s="66" t="inlineStr">
         <is>
-          <t>Competitor scraper / Chrome-extension ingestion can break or be abused</t>
+          <t>Validate ingested competitor rates (rate-shopper)</t>
         </is>
       </c>
       <c r="E33" s="65" t="inlineStr">
         <is>
-          <t>Rate-shopping data comes from the Chrome extension; if it stalls or sends bad data, pricing advice is built on stale/garbage rates.</t>
+          <t>Rate-shopping data comes from the Chrome extension; if it stalls or sends bad data, pricing advice rests on stale/garbage rates.
+⏱ When it surfaces: When the scraper breaks or a competitor site changes.</t>
         </is>
       </c>
       <c r="F33" s="65" t="inlineStr">
         <is>
-          <t>External ingestion with limited validation; advice consumes it directly.</t>
+          <t>External ingestion with limited validation.</t>
         </is>
       </c>
       <c r="G33" s="65" t="inlineStr">
@@ -3124,7 +3219,7 @@
           <t>Validate/timestamp ingested rates; flag stale data; bound ingestion volume.</t>
         </is>
       </c>
-      <c r="H33" s="72" t="inlineStr">
+      <c r="H33" s="71" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3145,7 +3240,7 @@
         </is>
       </c>
       <c r="L33" s="65" t="inlineStr"/>
-      <c r="M33" s="65" t="inlineStr"/>
+      <c r="M33" s="69" t="inlineStr"/>
       <c r="N33" s="65" t="inlineStr"/>
       <c r="O33" s="70">
         <f>IF(AND(K33&lt;&gt;"",M33&lt;&gt;""),M33-K33,"")</f>
@@ -3153,11 +3248,11 @@
       </c>
       <c r="P33" s="65" t="inlineStr">
         <is>
-          <t>AI gives wrong pricing recommendations from stale competitor data -&gt; lost RevPAR or underpricing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="90" customHeight="1" s="52">
+          <t>Keeps AI pricing recommendations based on fresh, sane data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="100" customHeight="1" s="52">
       <c r="A34" s="63" t="inlineStr">
         <is>
           <t>BE-031</t>
@@ -3175,27 +3270,28 @@
       </c>
       <c r="D34" s="66" t="inlineStr">
         <is>
-          <t>Webhook signature verification must not regress (Razorpay / Meta)</t>
+          <t>Keep payment webhook signature verification locked down</t>
         </is>
       </c>
       <c r="E34" s="65" t="inlineStr">
         <is>
-          <t>Payment confirmation trusts HMAC-verified webhooks; any regression in verification (or per-hotel key handling) enables spoofed 'paid' events.</t>
+          <t>Payment confirmation trusts HMAC-verified webhooks (Razorpay/Meta). This must stay correct as code evolves.
+⏱ When it surfaces: Only if a future change weakens verification.</t>
         </is>
       </c>
       <c r="F34" s="65" t="inlineStr">
         <is>
-          <t>Security-critical path that depends on correct HMAC checks staying in place.</t>
+          <t>Security-critical path that must not regress.</t>
         </is>
       </c>
       <c r="G34" s="65" t="inlineStr">
         <is>
-          <t>Lock down with tests asserting signature rejection; alert on verification failures; keep strict per-hotel keys.</t>
-        </is>
-      </c>
-      <c r="H34" s="71" t="inlineStr">
-        <is>
-          <t>Critical</t>
+          <t>Add tests asserting signature rejection; alert on verification failures; keep strict per-hotel keys.</t>
+        </is>
+      </c>
+      <c r="H34" s="67" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="I34" s="68" t="inlineStr">
@@ -3214,7 +3310,7 @@
         </is>
       </c>
       <c r="L34" s="65" t="inlineStr"/>
-      <c r="M34" s="65" t="inlineStr"/>
+      <c r="M34" s="69" t="inlineStr"/>
       <c r="N34" s="65" t="inlineStr"/>
       <c r="O34" s="70">
         <f>IF(AND(K34&lt;&gt;"",M34&lt;&gt;""),M34-K34,"")</f>
@@ -3222,11 +3318,11 @@
       </c>
       <c r="P34" s="65" t="inlineStr">
         <is>
-          <t>A spoofed webhook could mark unpaid bookings as paid -&gt; direct financial loss.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="90" customHeight="1" s="52">
+          <t>Protects directly against spoofed 'paid' events / financial loss.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="100" customHeight="1" s="52">
       <c r="A35" s="63" t="inlineStr">
         <is>
           <t>BE-032</t>
@@ -3244,27 +3340,28 @@
       </c>
       <c r="D35" s="66" t="inlineStr">
         <is>
-          <t>Tenant isolation in AI tools must not regress</t>
+          <t>Add automated tests for tenant isolation in AI tools</t>
         </is>
       </c>
       <c r="E35" s="65" t="inlineStr">
         <is>
-          <t>AI tools filter by user.hotel_id; dropping a filter in any tool would leak or mutate another hotel's data.</t>
+          <t>AI tools filter by user.hotel_id today; a future tool that forgets the filter would leak/modify another hotel's data.
+⏱ When it surfaces: Only if a future tool drops the hotel_id filter.</t>
         </is>
       </c>
       <c r="F35" s="65" t="inlineStr">
         <is>
-          <t>Isolation enforced per-query; easy to miss when adding a new tool.</t>
+          <t>Isolation enforced per-query; easy to miss on new tools.</t>
         </is>
       </c>
       <c r="G35" s="65" t="inlineStr">
         <is>
-          <t>Add a shared tenant-scoping helper + tests that assert cross-hotel access is blocked for every AI tool.</t>
-        </is>
-      </c>
-      <c r="H35" s="71" t="inlineStr">
-        <is>
-          <t>Critical</t>
+          <t>Add a shared tenant-scoping helper + tests asserting cross-hotel access is blocked for every AI tool.</t>
+        </is>
+      </c>
+      <c r="H35" s="67" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="I35" s="68" t="inlineStr">
@@ -3283,7 +3380,7 @@
         </is>
       </c>
       <c r="L35" s="65" t="inlineStr"/>
-      <c r="M35" s="65" t="inlineStr"/>
+      <c r="M35" s="69" t="inlineStr"/>
       <c r="N35" s="65" t="inlineStr"/>
       <c r="O35" s="70">
         <f>IF(AND(K35&lt;&gt;"",M35&lt;&gt;""),M35-K35,"")</f>
@@ -3291,11 +3388,11 @@
       </c>
       <c r="P35" s="65" t="inlineStr">
         <is>
-          <t>An IDOR in an AI tool would breach the core 'one hotel never sees another' guarantee -&gt; contractual and legal exposure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="90" customHeight="1" s="52">
+          <t>Locks in the core 'one hotel never sees another' guarantee against regressions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="100" customHeight="1" s="52">
       <c r="A36" s="63" t="inlineStr">
         <is>
           <t>BE-033</t>
@@ -3313,25 +3410,26 @@
       </c>
       <c r="D36" s="66" t="inlineStr">
         <is>
-          <t>PDF / report generation spikes worker memory under load</t>
+          <t>Offload report/PDF generation to a background worker</t>
         </is>
       </c>
       <c r="E36" s="65" t="inlineStr">
         <is>
-          <t>Reports load pandas/matplotlib/reportlab (lazy, but heavy). Concurrent report/PDF requests inflate per-worker RAM.</t>
+          <t>Reports load pandas/matplotlib/reportlab (lazy but heavy) in-request; concurrent exports inflate per-worker RAM.
+⏱ When it surfaces: When several hoteliers export analytics at once on a small box.</t>
         </is>
       </c>
       <c r="F36" s="65" t="inlineStr">
         <is>
-          <t>Heavy libraries loaded on demand per worker; CPU/RAM intensive.</t>
+          <t>Heavy, CPU/RAM-intensive work done in the request path.</t>
         </is>
       </c>
       <c r="G36" s="65" t="inlineStr">
         <is>
-          <t>Offload report generation to a background worker/queue; cap concurrent generations.</t>
-        </is>
-      </c>
-      <c r="H36" s="72" t="inlineStr">
+          <t>Move generation to a background worker/queue; cap concurrency.</t>
+        </is>
+      </c>
+      <c r="H36" s="71" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3343,7 +3441,7 @@
       </c>
       <c r="J36" s="65" t="inlineStr">
         <is>
-          <t>Backend Dev / DevOps</t>
+          <t>Backend Dev</t>
         </is>
       </c>
       <c r="K36" s="69" t="inlineStr">
@@ -3352,7 +3450,7 @@
         </is>
       </c>
       <c r="L36" s="65" t="inlineStr"/>
-      <c r="M36" s="65" t="inlineStr"/>
+      <c r="M36" s="69" t="inlineStr"/>
       <c r="N36" s="65" t="inlineStr"/>
       <c r="O36" s="70">
         <f>IF(AND(K36&lt;&gt;"",M36&lt;&gt;""),M36-K36,"")</f>
@@ -3360,11 +3458,11 @@
       </c>
       <c r="P36" s="65" t="inlineStr">
         <is>
-          <t>A few simultaneous report exports can OOM a small Railway box and restart workers, dropping in-flight requests.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="90" customHeight="1" s="52">
+          <t>Avoids worker OOM/restarts dropping in-flight requests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="100" customHeight="1" s="52">
       <c r="A37" s="63" t="inlineStr">
         <is>
           <t>BE-034</t>
@@ -3382,25 +3480,26 @@
       </c>
       <c r="D37" s="66" t="inlineStr">
         <is>
-          <t>Canned error messages hide real outages from monitoring</t>
+          <t>Alert when the AI falls back to its canned error message</t>
         </is>
       </c>
       <c r="E37" s="65" t="inlineStr">
         <is>
-          <t>On failure the bots return friendly text ('I'm having trouble connecting') with the error only in logs; without alerting, sustained failures look like normal traffic.</t>
+          <t>On failure the bots return friendly text and log the error; without alerting, sustained failures look like normal traffic.
+⏱ When it surfaces: During a quiet AI/provider outage.</t>
         </is>
       </c>
       <c r="F37" s="65" t="inlineStr">
         <is>
-          <t>Graceful degradation without a paired alert/metric.</t>
+          <t>Graceful degradation without a paired alert.</t>
         </is>
       </c>
       <c r="G37" s="65" t="inlineStr">
         <is>
-          <t>Emit an error metric whenever the canned fallback is used; alert on rate.</t>
-        </is>
-      </c>
-      <c r="H37" s="73" t="inlineStr">
+          <t>Emit an error metric whenever the canned fallback fires; alert on rate.</t>
+        </is>
+      </c>
+      <c r="H37" s="74" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -3412,7 +3511,7 @@
       </c>
       <c r="J37" s="65" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Backend Dev</t>
         </is>
       </c>
       <c r="K37" s="69" t="inlineStr">
@@ -3421,7 +3520,7 @@
         </is>
       </c>
       <c r="L37" s="65" t="inlineStr"/>
-      <c r="M37" s="65" t="inlineStr"/>
+      <c r="M37" s="69" t="inlineStr"/>
       <c r="N37" s="65" t="inlineStr"/>
       <c r="O37" s="70">
         <f>IF(AND(K37&lt;&gt;"",M37&lt;&gt;""),M37-K37,"")</f>
@@ -3429,7 +3528,7 @@
       </c>
       <c r="P37" s="65" t="inlineStr">
         <is>
-          <t>The AI can be down for hours while dashboards look green; discovered via customer complaints.</t>
+          <t>The AI can't be silently down for hours; issues surface before customers complain.</t>
         </is>
       </c>
     </row>
@@ -3462,242 +3561,242 @@
   <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" style="52" min="1" max="1"/>
-    <col width="34" customWidth="1" style="52" min="2" max="2"/>
-    <col width="46" customWidth="1" style="52" min="3" max="3"/>
-    <col width="40" customWidth="1" style="52" min="4" max="4"/>
+    <col width="24" customWidth="1" style="52" min="1" max="1"/>
+    <col width="30" customWidth="1" style="52" min="2" max="2"/>
+    <col width="44" customWidth="1" style="52" min="3" max="3"/>
+    <col width="38" customWidth="1" style="52" min="4" max="4"/>
     <col width="34" customWidth="1" style="52" min="5" max="5"/>
-    <col width="46" customWidth="1" style="52" min="6" max="6"/>
+    <col width="44" customWidth="1" style="52" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="76" t="inlineStr">
+      <c r="A1" s="75" t="inlineStr">
         <is>
           <t>⚡ Load, Abuse &amp; Cloud-Cost Scenarios — 'what happens if…'</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="77" t="inlineStr">
+      <c r="A2" s="76" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="B2" s="77" t="inlineStr">
+      <c r="B2" s="76" t="inlineStr">
         <is>
           <t>Trigger</t>
         </is>
       </c>
-      <c r="C2" s="77" t="inlineStr">
+      <c r="C2" s="76" t="inlineStr">
         <is>
           <t>What happens technically (code-grounded)</t>
         </is>
       </c>
-      <c r="D2" s="77" t="inlineStr">
+      <c r="D2" s="76" t="inlineStr">
         <is>
           <t>Business impact</t>
         </is>
       </c>
-      <c r="E2" s="77" t="inlineStr">
+      <c r="E2" s="76" t="inlineStr">
         <is>
           <t>Current safeguard</t>
         </is>
       </c>
-      <c r="F2" s="77" t="inlineStr">
-        <is>
-          <t>Gap / recommended fix</t>
+      <c r="F2" s="76" t="inlineStr">
+        <is>
+          <t>Recommended hardening</t>
         </is>
       </c>
     </row>
     <row r="3" ht="120" customHeight="1" s="52">
-      <c r="A3" s="78" t="inlineStr">
-        <is>
-          <t>100 users land on one hotel page at once</t>
-        </is>
-      </c>
-      <c r="B3" s="78" t="inlineStr">
-        <is>
-          <t>A campaign/QR/sale drives a burst of simultaneous visitors to one booking page.</t>
-        </is>
-      </c>
-      <c r="C3" s="78" t="inlineStr">
-        <is>
-          <t>Each visit can fire room search + availability + AI widget pre-warm. Availability does O(bookings*rooms) loops; AI chat holds a DB connection for the whole LLM call. Default pool is ~10 conns/worker (SCALE_TUNING.md).</t>
-        </is>
-      </c>
-      <c r="D3" s="78" t="inlineStr">
-        <is>
-          <t>Pool exhausts -&gt; requests queue/timeout -&gt; 500s for ALL hotels, not just this one. The 'success' of a campaign causes an outage.</t>
-        </is>
-      </c>
-      <c r="E3" s="78" t="inlineStr">
-        <is>
-          <t>Per-worker pool, lazy heavy imports, short caches, documented connection math.</t>
-        </is>
-      </c>
-      <c r="F3" s="78" t="inlineStr">
-        <is>
-          <t>Release DB session before LLM; SQL-aggregate availability; put a CDN/cache on public reads; right-size pool/concurrency; run the load test.</t>
+      <c r="A3" s="77" t="inlineStr">
+        <is>
+          <t>100 users on one hotel page at once</t>
+        </is>
+      </c>
+      <c r="B3" s="77" t="inlineStr">
+        <is>
+          <t>Campaign/QR/sale drives a burst to one page.</t>
+        </is>
+      </c>
+      <c r="C3" s="77" t="inlineStr">
+        <is>
+          <t>Each visit can fire room search + availability + AI widget warm. Availability counts in Python; AI chat holds a DB connection for the whole LLM call. Default pool ~10/worker.</t>
+        </is>
+      </c>
+      <c r="D3" s="77" t="inlineStr">
+        <is>
+          <t>If the pool saturates, requests queue/timeout -&gt; 500s for ALL hotels until it drains.</t>
+        </is>
+      </c>
+      <c r="E3" s="77" t="inlineStr">
+        <is>
+          <t>Per-worker pool, lazy heavy imports, short caches, documented connection math, 60-120/min public read limits.</t>
+        </is>
+      </c>
+      <c r="F3" s="77" t="inlineStr">
+        <is>
+          <t>Release DB session before the LLM call; CDN/cache public reads; right-size pool/concurrency; run the load test.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="120" customHeight="1" s="52">
-      <c r="A4" s="78" t="inlineStr">
+      <c r="A4" s="77" t="inlineStr">
         <is>
           <t>Bot spams the public AI chat</t>
         </is>
       </c>
-      <c r="B4" s="78" t="inlineStr">
-        <is>
-          <t>Anonymous attacker scripts /public/chat/guest, rotating X-Forwarded-For to dodge the IP limit.</t>
-        </is>
-      </c>
-      <c r="C4" s="78" t="inlineStr">
-        <is>
-          <t>5/min IP limit is spoofable; only backstop is 1000 LLM calls/hotel/day, which FAILS OPEN if Redis is down. Each message = 1-2 LLM calls; errors escalate to the 70B model.</t>
-        </is>
-      </c>
-      <c r="D4" s="78" t="inlineStr">
-        <is>
-          <t>Up to ~1000 paid LLM calls/day/hotel (unbounded if Redis down) -&gt; cloud/LLM invoice spike with zero revenue. Multiplied across hotels if attacked broadly.</t>
-        </is>
-      </c>
-      <c r="E4" s="78" t="inlineStr">
-        <is>
-          <t>Per-hotel daily cap (1000), feature flag, 5/min IP limit, cheap default model, token accounting.</t>
-        </is>
-      </c>
-      <c r="F4" s="78" t="inlineStr">
-        <is>
-          <t>Signed widget token/captcha; fail-CLOSED quota; platform-wide spend breaker; one cheap-model fallback only.</t>
+      <c r="B4" s="77" t="inlineStr">
+        <is>
+          <t>Anonymous attacker scripts the widget, rotating X-Forwarded-For.</t>
+        </is>
+      </c>
+      <c r="C4" s="77" t="inlineStr">
+        <is>
+          <t>5/min IP limit is spoofable; backstop is 1000 LLM calls/hotel/day, which fails open without Redis. Each message = 1-2 LLM calls.</t>
+        </is>
+      </c>
+      <c r="D4" s="77" t="inlineStr">
+        <is>
+          <t>Worst-case a few $/day of LLM per targeted hotel; bounded by the daily cap unless Redis is down.</t>
+        </is>
+      </c>
+      <c r="E4" s="77" t="inlineStr">
+        <is>
+          <t>Per-hotel daily cap (1000), feature flag, cheap 8B model, token accounting, fixed cheap fallback.</t>
+        </is>
+      </c>
+      <c r="F4" s="77" t="inlineStr">
+        <is>
+          <t>Signed widget token/captcha; fail-closed quota; platform-wide spend breaker.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="120" customHeight="1" s="52">
-      <c r="A5" s="78" t="inlineStr">
+      <c r="A5" s="77" t="inlineStr">
         <is>
           <t>Someone spams the backend auth</t>
         </is>
       </c>
-      <c r="B5" s="78" t="inlineStr">
-        <is>
-          <t>Flood of authenticated routes with garbage/expired Bearer tokens.</t>
-        </is>
-      </c>
-      <c r="C5" s="78" t="inlineStr">
-        <is>
-          <t>Login is on Supabase (no backend password endpoint), but invalid tokens are uncacheable, so every request runs verify_supabase_token (CPU + possible Supabase call). Most authenticated routes have NO rate limit.</t>
-        </is>
-      </c>
-      <c r="D5" s="78" t="inlineStr">
-        <is>
-          <t>CPU and Supabase auth load climb; latency degrades for real logged-in hoteliers; possible Supabase rate-limit/cost.</t>
-        </is>
-      </c>
-      <c r="E5" s="78" t="inlineStr">
-        <is>
-          <t>Token payloads cached (valid only); active-session tracking; Supabase verifies signatures &amp; exp.</t>
-        </is>
-      </c>
-      <c r="F5" s="78" t="inlineStr">
-        <is>
-          <t>Baseline IP+token rate limit on authenticated routes; short negative-cache for failed verifications; alert on auth-error spikes.</t>
+      <c r="B5" s="77" t="inlineStr">
+        <is>
+          <t>Flood of authenticated routes with garbage Bearer tokens.</t>
+        </is>
+      </c>
+      <c r="C5" s="77" t="inlineStr">
+        <is>
+          <t>Login is on Supabase (no backend password endpoint). Invalid tokens are uncacheable so each runs a JWT verify; most authed routes have no rate limit.</t>
+        </is>
+      </c>
+      <c r="D5" s="77" t="inlineStr">
+        <is>
+          <t>CPU + Supabase auth load climb; latency degrades for real hoteliers.</t>
+        </is>
+      </c>
+      <c r="E5" s="77" t="inlineStr">
+        <is>
+          <t>Valid-token payload caching; active-session tracking; Supabase verifies signature+exp; PII now logged at DEBUG.</t>
+        </is>
+      </c>
+      <c r="F5" s="77" t="inlineStr">
+        <is>
+          <t>Baseline IP+token limit on authed routes; short negative-cache; alert on auth-error spikes.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="120" customHeight="1" s="52">
-      <c r="A6" s="78" t="inlineStr">
-        <is>
-          <t>Redis goes down in production</t>
-        </is>
-      </c>
-      <c r="B6" s="78" t="inlineStr">
-        <is>
-          <t>Managed Redis blip or restart (single instance today).</t>
-        </is>
-      </c>
-      <c r="C6" s="78" t="inlineStr">
-        <is>
-          <t>Rate limits, AI per-hotel quota, auth cache, slug cache, analytics caches and payment idempotency all degrade; quota &amp; limits fail OPEN.</t>
-        </is>
-      </c>
-      <c r="D6" s="78" t="inlineStr">
-        <is>
-          <t>Abuse/cost protection vanishes exactly when the system is fragile; payment idempotency loss risks double-charges.</t>
-        </is>
-      </c>
-      <c r="E6" s="78" t="inlineStr">
-        <is>
-          <t>Best-effort try/except around Redis; app keeps serving.</t>
-        </is>
-      </c>
-      <c r="F6" s="78" t="inlineStr">
-        <is>
-          <t>Managed HA Redis; explicit fail-closed behaviour for cost/payment controls; Redis health alerting.</t>
+      <c r="A6" s="77" t="inlineStr">
+        <is>
+          <t>Redis goes down</t>
+        </is>
+      </c>
+      <c r="B6" s="77" t="inlineStr">
+        <is>
+          <t>Single Redis instance restarts/blips.</t>
+        </is>
+      </c>
+      <c r="C6" s="77" t="inlineStr">
+        <is>
+          <t>Rate limits, AI quota, auth cache, slug/analytics caches and payment idempotency degrade; quota+limits fail open.</t>
+        </is>
+      </c>
+      <c r="D6" s="77" t="inlineStr">
+        <is>
+          <t>Abuse/cost protection drops; payment idempotency loss risks double-charges.</t>
+        </is>
+      </c>
+      <c r="E6" s="77" t="inlineStr">
+        <is>
+          <t>Best-effort try/except keeps the app serving.</t>
+        </is>
+      </c>
+      <c r="F6" s="77" t="inlineStr">
+        <is>
+          <t>Managed HA Redis; explicit fail-closed for cost/payment controls; Redis health alerting.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="120" customHeight="1" s="52">
-      <c r="A7" s="78" t="inlineStr">
+      <c r="A7" s="77" t="inlineStr">
         <is>
           <t>AI adoption grows (marketing works)</t>
         </is>
       </c>
-      <c r="B7" s="78" t="inlineStr">
+      <c r="B7" s="77" t="inlineStr">
         <is>
           <t>More guests use the concierge across more hotels.</t>
         </is>
       </c>
-      <c r="C7" s="78" t="inlineStr">
-        <is>
-          <t>Variable cost = 1-2 LLM calls per message; cache hit-rate is limited (short TTL). Hotelier assistant currently defaults to a 70B model.</t>
-        </is>
-      </c>
-      <c r="D7" s="78" t="inlineStr">
-        <is>
-          <t>Cloud/LLM bill grows with traffic, not revenue; margins compress as usage rises.</t>
-        </is>
-      </c>
-      <c r="E7" s="78" t="inlineStr">
-        <is>
-          <t>Cheap 8B default on guest bot, history capped to 20, tool/token caps, usage counters.</t>
-        </is>
-      </c>
-      <c r="F7" s="78" t="inlineStr">
-        <is>
-          <t>Cheap default everywhere except analytics; raise cache hit-rate; per-tier budget + auto-throttle; bill pass-through decision.</t>
+      <c r="C7" s="77" t="inlineStr">
+        <is>
+          <t>Variable cost = 1-2 LLM calls/message; limited dedup (short cache).</t>
+        </is>
+      </c>
+      <c r="D7" s="77" t="inlineStr">
+        <is>
+          <t>LLM bill grows with traffic; margins compress without a budget.</t>
+        </is>
+      </c>
+      <c r="E7" s="77" t="inlineStr">
+        <is>
+          <t>Cheap 8B default on guest bot, history capped at 20, tool/token caps, usage counters.</t>
+        </is>
+      </c>
+      <c r="F7" s="77" t="inlineStr">
+        <is>
+          <t>Per-tier budget + auto-throttle; higher cache hit-rate; bill pass-through decision.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="120" customHeight="1" s="52">
-      <c r="A8" s="78" t="inlineStr">
+      <c r="A8" s="77" t="inlineStr">
         <is>
           <t>Concurrent report/PDF exports</t>
         </is>
       </c>
-      <c r="B8" s="78" t="inlineStr">
-        <is>
-          <t>Several hoteliers export PDF/Excel analytics at once.</t>
-        </is>
-      </c>
-      <c r="C8" s="78" t="inlineStr">
-        <is>
-          <t>pandas/matplotlib/reportlab load per worker (lazy but heavy); CPU/RAM intensive; runs in-request.</t>
-        </is>
-      </c>
-      <c r="D8" s="78" t="inlineStr">
-        <is>
-          <t>Small boxes can OOM and restart workers, dropping in-flight requests for everyone on that worker.</t>
-        </is>
-      </c>
-      <c r="E8" s="78" t="inlineStr">
+      <c r="B8" s="77" t="inlineStr">
+        <is>
+          <t>Several hoteliers export analytics at once.</t>
+        </is>
+      </c>
+      <c r="C8" s="77" t="inlineStr">
+        <is>
+          <t>pandas/matplotlib/reportlab load per worker (lazy but heavy); CPU/RAM intensive in-request.</t>
+        </is>
+      </c>
+      <c r="D8" s="77" t="inlineStr">
+        <is>
+          <t>Small boxes can OOM and restart workers, dropping in-flight requests.</t>
+        </is>
+      </c>
+      <c r="E8" s="77" t="inlineStr">
         <is>
           <t>Lazy imports keep idle RAM low.</t>
         </is>
       </c>
-      <c r="F8" s="78" t="inlineStr">
-        <is>
-          <t>Move report generation to a background worker/queue; cap concurrent generations.</t>
+      <c r="F8" s="77" t="inlineStr">
+        <is>
+          <t>Background worker/queue for generation; cap concurrent exports.</t>
         </is>
       </c>
     </row>
@@ -3715,114 +3814,281 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" style="52" min="1" max="1"/>
-    <col width="52" customWidth="1" style="52" min="2" max="2"/>
-    <col width="52" customWidth="1" style="52" min="3" max="3"/>
-    <col width="60" customWidth="1" style="52" min="4" max="4"/>
+    <col width="16" customWidth="1" style="52" min="1" max="1"/>
+    <col width="34" customWidth="1" style="52" min="2" max="2"/>
+    <col width="46" customWidth="1" style="52" min="3" max="3"/>
+    <col width="50" customWidth="1" style="52" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="76" t="inlineStr">
-        <is>
-          <t>👥 Team &amp; Hiring Recommendation</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="70" customHeight="1" s="52">
+      <c r="A1" s="75" t="inlineStr">
+        <is>
+          <t>🔄 CI/CD Pipeline — automated quality gates</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="45" customHeight="1" s="52">
       <c r="A2" s="78" t="inlineStr">
         <is>
-          <t>Recommendation: YES — hire one Backend Engineer (priority) and one Frontend Engineer. The codebase is large (~70 routers, 250+ endpoints, payments, multi-tenant, AI) and several Critical issues (AI feature down, pool-exhaustion outage risk, prompt-injection on money actions) are currently unowned. A senior backend hire is the highest-leverage action; the Critical AI-crash bug alone is a same-day fix once owned.</t>
+          <t>GitHub Actions runs on every Pull Request and on pushes to main/develop/feature branches. A change cannot merge unless these gates pass — this is what stops a bug like the AI-assistant crash from ever reaching production again.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="77" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="B3" s="77" t="inlineStr">
-        <is>
-          <t>Why needed (tied to issues)</t>
-        </is>
-      </c>
-      <c r="C3" s="77" t="inlineStr">
-        <is>
-          <t>What they own in THIS project</t>
-        </is>
-      </c>
-      <c r="D3" s="77" t="inlineStr">
-        <is>
-          <t>First 30/60/90 days</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="150" customHeight="1" s="52">
+      <c r="A3" s="76" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="B3" s="76" t="inlineStr">
+        <is>
+          <t>Tool / Action</t>
+        </is>
+      </c>
+      <c r="C3" s="76" t="inlineStr">
+        <is>
+          <t>What it checks</t>
+        </is>
+      </c>
+      <c r="D3" s="76" t="inlineStr">
+        <is>
+          <t>Why it matters here</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1" s="52">
       <c r="A4" s="79" t="inlineStr">
         <is>
-          <t>Backend Engineer (Python/FastAPI) — PRIORITY HIRE</t>
-        </is>
-      </c>
-      <c r="B4" s="78" t="inlineStr">
-        <is>
-          <t>Owns the Critical/High backend issues: AI assistant crash (BE-007), DB connection held during LLM (BE-008), prompt-injection &amp; code-level confirmation on mutating tools (BE-011/012), cost (fallback/model choice BE-009/019), auth abuse &amp; rate limiting (BE-026), tenant isolation (BE-032), webhook integrity (BE-031).</t>
-        </is>
-      </c>
-      <c r="C4" s="78" t="inlineStr">
-        <is>
-          <t>FastAPI services, AI agents (agno), SQLModel/Postgres performance &amp; indexing, Redis, payments/Razorpay, multi-tenant security, rate limiting/abuse, cost controls, tests, observability.</t>
-        </is>
-      </c>
-      <c r="D4" s="78" t="inlineStr">
-        <is>
-          <t>30d: fix AI crash + add smoke tests; release DB session before LLM; baseline rate limits. 60d: prompt-injection hardening, code-enforced confirmations, SQL-aggregate availability + indexes, fail-closed quota. 90d: cost dashboards/alerts, Redis HA rollout, load test + scaling tune, CI test coverage for AI paths.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="150" customHeight="1" s="52">
+          <t>Trigger</t>
+        </is>
+      </c>
+      <c r="B4" s="77" t="inlineStr">
+        <is>
+          <t>GitHub Actions (push + pull_request)</t>
+        </is>
+      </c>
+      <c r="C4" s="77" t="inlineStr">
+        <is>
+          <t>Runs automatically on PRs and branch pushes (main/develop/claude/**).</t>
+        </is>
+      </c>
+      <c r="D4" s="77" t="inlineStr">
+        <is>
+          <t>Every change is checked before merge, not after deploy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1" s="52">
       <c r="A5" s="79" t="inlineStr">
         <is>
-          <t>Frontend Engineer (React/Vite)</t>
-        </is>
-      </c>
-      <c r="B5" s="78" t="inlineStr">
-        <is>
-          <t>Owns the guest-facing booking experience and the hotelier dashboard quality: chart pipeline reliability (BE-016), AI chat/streaming UX, error &amp; loading states so backend failures degrade gracefully, and conversion-critical booking flow.</t>
-        </is>
-      </c>
-      <c r="C5" s="78" t="inlineStr">
-        <is>
-          <t>React/Vite app, booking engine UI, AI chat widget + SSE streaming UI, analytics charts, error/empty/loading states, accessibility, performance (bundle size, lazy loading), and frontend telemetry.</t>
-        </is>
-      </c>
-      <c r="D5" s="78" t="inlineStr">
-        <is>
-          <t>30d: robust error/loading states for AI + booking; fix chart rendering pipeline. 60d: streaming chat UX + disconnect handling; conversion polish on the booking funnel. 90d: performance pass (bundle/CDN), accessibility, and frontend analytics for funnel drop-off.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="150" customHeight="1" s="52">
+          <t>Backend - Install</t>
+        </is>
+      </c>
+      <c r="B5" s="77" t="inlineStr">
+        <is>
+          <t>pip install -r requirements.txt (Python 3.11)</t>
+        </is>
+      </c>
+      <c r="C5" s="77" t="inlineStr">
+        <is>
+          <t>Dependencies resolve and install cleanly.</t>
+        </is>
+      </c>
+      <c r="D5" s="77" t="inlineStr">
+        <is>
+          <t>Catches broken/missing dependencies early.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1" s="52">
       <c r="A6" s="79" t="inlineStr">
         <is>
-          <t>(Optional) Part-time DevOps / SRE</t>
-        </is>
-      </c>
-      <c r="B6" s="78" t="inlineStr">
-        <is>
-          <t>Several issues are infra: Redis HA/SPOF (BE-026), pool exhaustion (BE-023), trusted-proxy/WAF (BE-002/025), scaling tune &amp; load test (BE-004), report worker/queue (BE-033).</t>
-        </is>
-      </c>
-      <c r="C6" s="78" t="inlineStr">
-        <is>
-          <t>Railway/infra, Supabase connection budget, Redis HA, CDN/WAF, monitoring &amp; alerting (Sentry), CI/CD, load testing.</t>
-        </is>
-      </c>
-      <c r="D6" s="78" t="inlineStr">
-        <is>
-          <t>Can be a fractional/contract hire or absorbed by the senior backend engineer initially; formalise before scaling traffic.</t>
+          <t>Backend - Compile</t>
+        </is>
+      </c>
+      <c r="B6" s="77" t="inlineStr">
+        <is>
+          <t>python -m compileall app main.py</t>
+        </is>
+      </c>
+      <c r="C6" s="77" t="inlineStr">
+        <is>
+          <t>Fast-fails on any syntax or import error across the backend.</t>
+        </is>
+      </c>
+      <c r="D6" s="77" t="inlineStr">
+        <is>
+          <t>Would have instantly caught the missing-logger class of bug.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1" s="52">
+      <c r="A7" s="79" t="inlineStr">
+        <is>
+          <t>Backend - Tests</t>
+        </is>
+      </c>
+      <c r="B7" s="77" t="inlineStr">
+        <is>
+          <t>pytest tests/ (253 passing)</t>
+        </is>
+      </c>
+      <c r="C7" s="77" t="inlineStr">
+        <is>
+          <t>Runs the full backend suite incl. the new AI smoke/regression tests.</t>
+        </is>
+      </c>
+      <c r="D7" s="77" t="inlineStr">
+        <is>
+          <t>Pins the AI-assistant fix and guards multi-tenant/payment behaviour.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1" s="52">
+      <c r="A8" s="79" t="inlineStr">
+        <is>
+          <t>Frontend - Types</t>
+        </is>
+      </c>
+      <c r="B8" s="77" t="inlineStr">
+        <is>
+          <t>tsc --noEmit</t>
+        </is>
+      </c>
+      <c r="C8" s="77" t="inlineStr">
+        <is>
+          <t>TypeScript type-checks the whole frontend.</t>
+        </is>
+      </c>
+      <c r="D8" s="77" t="inlineStr">
+        <is>
+          <t>Catches UI/data-shape errors before build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1" s="52">
+      <c r="A9" s="79" t="inlineStr">
+        <is>
+          <t>Frontend - Build</t>
+        </is>
+      </c>
+      <c r="B9" s="77" t="inlineStr">
+        <is>
+          <t>npm run build (Vite)</t>
+        </is>
+      </c>
+      <c r="C9" s="77" t="inlineStr">
+        <is>
+          <t>Production build succeeds.</t>
+        </is>
+      </c>
+      <c r="D9" s="77" t="inlineStr">
+        <is>
+          <t>Ensures the app actually ships.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1" s="52">
+      <c r="A10" s="79" t="inlineStr">
+        <is>
+          <t>Frontend - E2E</t>
+        </is>
+      </c>
+      <c r="B10" s="77" t="inlineStr">
+        <is>
+          <t>Playwright (chromium)</t>
+        </is>
+      </c>
+      <c r="C10" s="77" t="inlineStr">
+        <is>
+          <t>End-to-end browser tests of key flows.</t>
+        </is>
+      </c>
+      <c r="D10" s="77" t="inlineStr">
+        <is>
+          <t>Verifies real user journeys (incl. booking/AI UI).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1" s="52">
+      <c r="A11" s="79" t="inlineStr">
+        <is>
+          <t>Artifacts</t>
+        </is>
+      </c>
+      <c r="B11" s="77" t="inlineStr">
+        <is>
+          <t>upload-artifact</t>
+        </is>
+      </c>
+      <c r="C11" s="77" t="inlineStr">
+        <is>
+          <t>Stores the Playwright report for 30 days.</t>
+        </is>
+      </c>
+      <c r="D11" s="77" t="inlineStr">
+        <is>
+          <t>Failures are debuggable from the PR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1" s="52">
+      <c r="A12" s="79" t="inlineStr">
+        <is>
+          <t>Deploy (CD)</t>
+        </is>
+      </c>
+      <c r="B12" s="77" t="inlineStr">
+        <is>
+          <t>Railway (create_all on boot)</t>
+        </is>
+      </c>
+      <c r="C12" s="77" t="inlineStr">
+        <is>
+          <t>Deploys backend+frontend; DB tables via create_all.</t>
+        </is>
+      </c>
+      <c r="D12" s="77" t="inlineStr">
+        <is>
+          <t>Roadmap: add a staging gate + smoke check before prod promotion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="80" t="inlineStr">
+        <is>
+          <t>Recommended next CI/CD additions</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. Add pip-audit / npm audit (dependency vulnerability scan) as a non-blocking gate, then enforce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. Add a staging environment + automated smoke test before promoting to production (true CD).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. Add coverage reporting and a minimum threshold so AI/payment paths stay tested.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. Add a secrets-scanning step (e.g. gitleaks) to prevent keys being committed.</t>
         </is>
       </c>
     </row>
@@ -3841,6 +4107,132 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" style="52" min="1" max="1"/>
+    <col width="52" customWidth="1" style="52" min="2" max="2"/>
+    <col width="52" customWidth="1" style="52" min="3" max="3"/>
+    <col width="58" customWidth="1" style="52" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="75" t="inlineStr">
+        <is>
+          <t>👥 Team &amp; Hiring Recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1" s="52">
+      <c r="A2" s="78" t="inlineStr">
+        <is>
+          <t>Recommendation: YES — hire one Backend Engineer (priority) and one Frontend Engineer. The platform is large (~70 routers, 250+ endpoints, payments, multi-tenant, AI). The critical AI-assistant bug is already fixed; the remaining roadmap is mostly backend reliability/cost/security plus frontend UX/perf. Dedicated owners make the Hypercare SLAs achievable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="76" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="B3" s="76" t="inlineStr">
+        <is>
+          <t>Why needed (tied to issues)</t>
+        </is>
+      </c>
+      <c r="C3" s="76" t="inlineStr">
+        <is>
+          <t>What they own in THIS project</t>
+        </is>
+      </c>
+      <c r="D3" s="76" t="inlineStr">
+        <is>
+          <t>First 30 / 60 / 90 days</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="150" customHeight="1" s="52">
+      <c r="A4" s="79" t="inlineStr">
+        <is>
+          <t>Backend Engineer (Python/FastAPI) — PRIORITY</t>
+        </is>
+      </c>
+      <c r="B4" s="82" t="inlineStr">
+        <is>
+          <t>Owns the High/Medium backend roadmap: DB session held during LLM (BE-008), code-level confirmation on mutating tools (BE-011), prompt-injection hardening (BE-012), AI abuse/rate limits (BE-024/025), Redis HA (BE-026), tenant-isolation tests (BE-032), webhook integrity (BE-031).</t>
+        </is>
+      </c>
+      <c r="C4" s="82" t="inlineStr">
+        <is>
+          <t>FastAPI services, AI agents (agno), Postgres performance &amp; indexing, Redis, payments/Razorpay, multi-tenant security, rate limiting, cost controls, tests, observability.</t>
+        </is>
+      </c>
+      <c r="D4" s="82" t="inlineStr">
+        <is>
+          <t>30d: rate-limit authed routes, ship fail-closed AI quota. 60d: release DB session before LLM, prompt-injection + code confirmations, SQL-aggregate availability. 90d: cost alerts/auto-throttle, Redis HA, load test + scaling tune.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="150" customHeight="1" s="52">
+      <c r="A5" s="79" t="inlineStr">
+        <is>
+          <t>Frontend Engineer (React/Vite)</t>
+        </is>
+      </c>
+      <c r="B5" s="82" t="inlineStr">
+        <is>
+          <t>Owns the guest booking experience and hotelier dashboard quality: chart pipeline (BE-016), AI chat/streaming UX, graceful error/loading states, and the conversion-critical booking funnel.</t>
+        </is>
+      </c>
+      <c r="C5" s="82" t="inlineStr">
+        <is>
+          <t>React/Vite app, booking engine UI, AI chat widget + SSE streaming UI, analytics charts, error/empty/loading states, accessibility, performance (bundle/CDN), frontend telemetry.</t>
+        </is>
+      </c>
+      <c r="D5" s="82" t="inlineStr">
+        <is>
+          <t>30d: robust error/loading states for AI + booking; fix chart rendering. 60d: streaming UX + disconnect handling; booking funnel polish. 90d: performance + accessibility pass; funnel drop-off analytics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="150" customHeight="1" s="52">
+      <c r="A6" s="79" t="inlineStr">
+        <is>
+          <t>(Optional) Fractional DevOps / SRE</t>
+        </is>
+      </c>
+      <c r="B6" s="82" t="inlineStr">
+        <is>
+          <t>Infra-flavoured items: Redis HA (BE-026), pool exhaustion (BE-023), trusted proxy/WAF (BE-002/024), load test (BE-004), report worker (BE-033).</t>
+        </is>
+      </c>
+      <c r="C6" s="82" t="inlineStr">
+        <is>
+          <t>Railway/infra, Supabase connection budget, Redis HA, CDN/WAF, monitoring/alerting (Sentry), CI/CD, load testing.</t>
+        </is>
+      </c>
+      <c r="D6" s="82" t="inlineStr">
+        <is>
+          <t>Can be contract or absorbed by the senior backend hire initially; formalise before scaling traffic.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
@@ -3849,7 +4241,7 @@
     <col width="20" customWidth="1" style="52" min="3" max="3"/>
     <col width="14" customWidth="1" style="52" min="4" max="5"/>
     <col width="16" customWidth="1" style="52" min="6" max="7"/>
-    <col width="18" customWidth="1" style="52" min="8" max="8"/>
+    <col width="20" customWidth="1" style="52" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" s="52">
@@ -3902,7 +4294,7 @@
       </c>
     </row>
     <row r="3" ht="36" customHeight="1" s="52">
-      <c r="A3" s="80" t="inlineStr">
+      <c r="A3" s="97" t="inlineStr">
         <is>
           <t>Pre-Development</t>
         </is>
@@ -3928,33 +4320,33 @@
       <c r="H3" s="65" t="inlineStr"/>
     </row>
     <row r="4" ht="36" customHeight="1" s="52">
-      <c r="A4" s="80" t="inlineStr">
+      <c r="A4" s="97" t="inlineStr">
         <is>
           <t>Pre-Development</t>
         </is>
       </c>
-      <c r="B4" s="81" t="inlineStr">
+      <c r="B4" s="98" t="inlineStr">
         <is>
           <t>Capacity plan + DB connection budget vs Supabase limit</t>
         </is>
       </c>
-      <c r="C4" s="82" t="inlineStr">
+      <c r="C4" s="99" t="inlineStr">
         <is>
           <t>Backend Dev</t>
         </is>
       </c>
-      <c r="D4" s="82" t="inlineStr"/>
-      <c r="E4" s="82" t="inlineStr"/>
-      <c r="F4" s="82" t="inlineStr"/>
-      <c r="G4" s="82" t="inlineStr">
+      <c r="D4" s="99" t="inlineStr"/>
+      <c r="E4" s="99" t="inlineStr"/>
+      <c r="F4" s="99" t="inlineStr"/>
+      <c r="G4" s="99" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="H4" s="81" t="inlineStr"/>
+      <c r="H4" s="98" t="inlineStr"/>
     </row>
     <row r="5" ht="36" customHeight="1" s="52">
-      <c r="A5" s="80" t="inlineStr">
+      <c r="A5" s="97" t="inlineStr">
         <is>
           <t>Pre-Development</t>
         </is>
@@ -3980,37 +4372,37 @@
       <c r="H5" s="65" t="inlineStr"/>
     </row>
     <row r="6" ht="36" customHeight="1" s="52">
-      <c r="A6" s="80" t="inlineStr">
+      <c r="A6" s="97" t="inlineStr">
         <is>
           <t>Pre-Development</t>
         </is>
       </c>
-      <c r="B6" s="81" t="inlineStr">
+      <c r="B6" s="98" t="inlineStr">
         <is>
           <t>Hiring: backend + frontend engineers</t>
         </is>
       </c>
-      <c r="C6" s="82" t="inlineStr">
+      <c r="C6" s="99" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="D6" s="82" t="inlineStr"/>
-      <c r="E6" s="82" t="inlineStr"/>
-      <c r="F6" s="82" t="inlineStr"/>
-      <c r="G6" s="82" t="inlineStr">
+      <c r="D6" s="99" t="inlineStr"/>
+      <c r="E6" s="99" t="inlineStr"/>
+      <c r="F6" s="99" t="inlineStr"/>
+      <c r="G6" s="99" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="H6" s="81" t="inlineStr">
+      <c r="H6" s="98" t="inlineStr">
         <is>
           <t>See Team sheet</t>
         </is>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1" s="52">
-      <c r="A7" s="80" t="inlineStr">
+      <c r="A7" s="97" t="inlineStr">
         <is>
           <t>Pre-Development</t>
         </is>
@@ -4036,96 +4428,140 @@
       <c r="H7" s="65" t="inlineStr"/>
     </row>
     <row r="8" ht="36" customHeight="1" s="52">
-      <c r="A8" s="83" t="inlineStr">
+      <c r="A8" s="94" t="inlineStr">
         <is>
           <t>Development</t>
         </is>
       </c>
-      <c r="B8" s="81" t="inlineStr">
+      <c r="B8" s="98" t="inlineStr">
         <is>
           <t>Fix AI assistant crash (logger) + smoke tests</t>
         </is>
       </c>
-      <c r="C8" s="82" t="inlineStr">
+      <c r="C8" s="99" t="inlineStr">
         <is>
           <t>Backend Dev</t>
         </is>
       </c>
-      <c r="D8" s="82" t="inlineStr"/>
-      <c r="E8" s="82" t="inlineStr"/>
-      <c r="F8" s="82" t="inlineStr"/>
-      <c r="G8" s="82" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="H8" s="81" t="inlineStr">
-        <is>
-          <t>Critical</t>
+      <c r="D8" s="99" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="E8" s="99" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="F8" s="99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="99" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H8" s="98" t="inlineStr">
+        <is>
+          <t>DONE - 253 tests green</t>
         </is>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" s="52">
-      <c r="A9" s="83" t="inlineStr">
+      <c r="A9" s="94" t="inlineStr">
         <is>
           <t>Development</t>
         </is>
       </c>
       <c r="B9" s="65" t="inlineStr">
         <is>
+          <t>Cheap-model error fallback + web-search timeout</t>
+        </is>
+      </c>
+      <c r="C9" s="69" t="inlineStr">
+        <is>
+          <t>Backend Dev</t>
+        </is>
+      </c>
+      <c r="D9" s="69" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="E9" s="69" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="F9" s="69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" s="69" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H9" s="65" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1" s="52">
+      <c r="A10" s="94" t="inlineStr">
+        <is>
+          <t>Development</t>
+        </is>
+      </c>
+      <c r="B10" s="98" t="inlineStr">
+        <is>
+          <t>Sanitise error responses + PII logging to DEBUG</t>
+        </is>
+      </c>
+      <c r="C10" s="99" t="inlineStr">
+        <is>
+          <t>Backend Dev</t>
+        </is>
+      </c>
+      <c r="D10" s="99" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="E10" s="99" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="F10" s="99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="99" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H10" s="98" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1" s="52">
+      <c r="A11" s="94" t="inlineStr">
+        <is>
+          <t>Development</t>
+        </is>
+      </c>
+      <c r="B11" s="65" t="inlineStr">
+        <is>
           <t>Release DB session before LLM round-trip</t>
-        </is>
-      </c>
-      <c r="C9" s="69" t="inlineStr">
-        <is>
-          <t>Backend Dev</t>
-        </is>
-      </c>
-      <c r="D9" s="69" t="inlineStr"/>
-      <c r="E9" s="69" t="inlineStr"/>
-      <c r="F9" s="69" t="inlineStr"/>
-      <c r="G9" s="69" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H9" s="65" t="inlineStr"/>
-    </row>
-    <row r="10" ht="36" customHeight="1" s="52">
-      <c r="A10" s="83" t="inlineStr">
-        <is>
-          <t>Development</t>
-        </is>
-      </c>
-      <c r="B10" s="81" t="inlineStr">
-        <is>
-          <t>Enforce code-level confirmation on mutating AI tools</t>
-        </is>
-      </c>
-      <c r="C10" s="82" t="inlineStr">
-        <is>
-          <t>Backend Dev</t>
-        </is>
-      </c>
-      <c r="D10" s="82" t="inlineStr"/>
-      <c r="E10" s="82" t="inlineStr"/>
-      <c r="F10" s="82" t="inlineStr"/>
-      <c r="G10" s="82" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H10" s="81" t="inlineStr"/>
-    </row>
-    <row r="11" ht="36" customHeight="1" s="52">
-      <c r="A11" s="83" t="inlineStr">
-        <is>
-          <t>Development</t>
-        </is>
-      </c>
-      <c r="B11" s="65" t="inlineStr">
-        <is>
-          <t>Prompt-injection hardening + tenant-scope tests</t>
         </is>
       </c>
       <c r="C11" s="69" t="inlineStr">
@@ -4144,33 +4580,33 @@
       <c r="H11" s="65" t="inlineStr"/>
     </row>
     <row r="12" ht="36" customHeight="1" s="52">
-      <c r="A12" s="83" t="inlineStr">
+      <c r="A12" s="94" t="inlineStr">
         <is>
           <t>Development</t>
         </is>
       </c>
-      <c r="B12" s="81" t="inlineStr">
-        <is>
-          <t>Cost: cheap-model default + fallback fix + caching</t>
-        </is>
-      </c>
-      <c r="C12" s="82" t="inlineStr">
+      <c r="B12" s="98" t="inlineStr">
+        <is>
+          <t>Prompt-injection hardening + code-level confirmations</t>
+        </is>
+      </c>
+      <c r="C12" s="99" t="inlineStr">
         <is>
           <t>Backend Dev</t>
         </is>
       </c>
-      <c r="D12" s="82" t="inlineStr"/>
-      <c r="E12" s="82" t="inlineStr"/>
-      <c r="F12" s="82" t="inlineStr"/>
-      <c r="G12" s="82" t="inlineStr">
+      <c r="D12" s="99" t="inlineStr"/>
+      <c r="E12" s="99" t="inlineStr"/>
+      <c r="F12" s="99" t="inlineStr"/>
+      <c r="G12" s="99" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="H12" s="81" t="inlineStr"/>
+      <c r="H12" s="98" t="inlineStr"/>
     </row>
     <row r="13" ht="36" customHeight="1" s="52">
-      <c r="A13" s="83" t="inlineStr">
+      <c r="A13" s="94" t="inlineStr">
         <is>
           <t>Development</t>
         </is>
@@ -4196,45 +4632,45 @@
       <c r="H13" s="65" t="inlineStr"/>
     </row>
     <row r="14" ht="36" customHeight="1" s="52">
-      <c r="A14" s="83" t="inlineStr">
+      <c r="A14" s="94" t="inlineStr">
         <is>
           <t>Development</t>
         </is>
       </c>
-      <c r="B14" s="81" t="inlineStr">
-        <is>
-          <t>Frontend: chart pipeline, error states, loading UX</t>
-        </is>
-      </c>
-      <c r="C14" s="82" t="inlineStr">
+      <c r="B14" s="98" t="inlineStr">
+        <is>
+          <t>Frontend: chart pipeline, error/loading UX</t>
+        </is>
+      </c>
+      <c r="C14" s="99" t="inlineStr">
         <is>
           <t>Frontend Dev</t>
         </is>
       </c>
-      <c r="D14" s="82" t="inlineStr"/>
-      <c r="E14" s="82" t="inlineStr"/>
-      <c r="F14" s="82" t="inlineStr"/>
-      <c r="G14" s="82" t="inlineStr">
+      <c r="D14" s="99" t="inlineStr"/>
+      <c r="E14" s="99" t="inlineStr"/>
+      <c r="F14" s="99" t="inlineStr"/>
+      <c r="G14" s="99" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="H14" s="81" t="inlineStr"/>
+      <c r="H14" s="98" t="inlineStr"/>
     </row>
     <row r="15" ht="36" customHeight="1" s="52">
-      <c r="A15" s="83" t="inlineStr">
+      <c r="A15" s="94" t="inlineStr">
         <is>
           <t>Development</t>
         </is>
       </c>
       <c r="B15" s="65" t="inlineStr">
         <is>
-          <t>Logging/PII hygiene + error-message sanitisation</t>
+          <t>QA + automated coverage for AI/payment paths</t>
         </is>
       </c>
       <c r="C15" s="69" t="inlineStr">
         <is>
-          <t>Backend Dev</t>
+          <t>Both Devs</t>
         </is>
       </c>
       <c r="D15" s="69" t="inlineStr"/>
@@ -4248,45 +4684,45 @@
       <c r="H15" s="65" t="inlineStr"/>
     </row>
     <row r="16" ht="36" customHeight="1" s="52">
-      <c r="A16" s="83" t="inlineStr">
-        <is>
-          <t>Development</t>
-        </is>
-      </c>
-      <c r="B16" s="81" t="inlineStr">
-        <is>
-          <t>QA pass + automated test coverage for AI paths</t>
-        </is>
-      </c>
-      <c r="C16" s="82" t="inlineStr">
-        <is>
-          <t>Both Devs</t>
-        </is>
-      </c>
-      <c r="D16" s="82" t="inlineStr"/>
-      <c r="E16" s="82" t="inlineStr"/>
-      <c r="F16" s="82" t="inlineStr"/>
-      <c r="G16" s="82" t="inlineStr">
+      <c r="A16" s="94" t="inlineStr">
+        <is>
+          <t>Post-Development</t>
+        </is>
+      </c>
+      <c r="B16" s="98" t="inlineStr">
+        <is>
+          <t>Redis HA + fail-closed quota</t>
+        </is>
+      </c>
+      <c r="C16" s="99" t="inlineStr">
+        <is>
+          <t>DevOps</t>
+        </is>
+      </c>
+      <c r="D16" s="99" t="inlineStr"/>
+      <c r="E16" s="99" t="inlineStr"/>
+      <c r="F16" s="99" t="inlineStr"/>
+      <c r="G16" s="99" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="H16" s="81" t="inlineStr"/>
+      <c r="H16" s="98" t="inlineStr"/>
     </row>
     <row r="17" ht="36" customHeight="1" s="52">
-      <c r="A17" s="84" t="inlineStr">
+      <c r="A17" s="100" t="inlineStr">
         <is>
           <t>Post-Development</t>
         </is>
       </c>
       <c r="B17" s="65" t="inlineStr">
         <is>
-          <t>Redis HA + fail-closed quota rollout</t>
+          <t>Cost monitoring + per-hotel spend alerts</t>
         </is>
       </c>
       <c r="C17" s="69" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Backend Dev</t>
         </is>
       </c>
       <c r="D17" s="69" t="inlineStr"/>
@@ -4300,45 +4736,45 @@
       <c r="H17" s="65" t="inlineStr"/>
     </row>
     <row r="18" ht="36" customHeight="1" s="52">
-      <c r="A18" s="84" t="inlineStr">
+      <c r="A18" s="100" t="inlineStr">
         <is>
           <t>Post-Development</t>
         </is>
       </c>
-      <c r="B18" s="81" t="inlineStr">
-        <is>
-          <t>Cost monitoring + per-hotel spend alerts</t>
-        </is>
-      </c>
-      <c r="C18" s="82" t="inlineStr">
+      <c r="B18" s="98" t="inlineStr">
+        <is>
+          <t>WAF / signed widget token / captcha for public AI</t>
+        </is>
+      </c>
+      <c r="C18" s="99" t="inlineStr">
         <is>
           <t>Backend Dev</t>
         </is>
       </c>
-      <c r="D18" s="82" t="inlineStr"/>
-      <c r="E18" s="82" t="inlineStr"/>
-      <c r="F18" s="82" t="inlineStr"/>
-      <c r="G18" s="82" t="inlineStr">
+      <c r="D18" s="99" t="inlineStr"/>
+      <c r="E18" s="99" t="inlineStr"/>
+      <c r="F18" s="99" t="inlineStr"/>
+      <c r="G18" s="99" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="H18" s="81" t="inlineStr"/>
+      <c r="H18" s="98" t="inlineStr"/>
     </row>
     <row r="19" ht="36" customHeight="1" s="52">
-      <c r="A19" s="84" t="inlineStr">
+      <c r="A19" s="100" t="inlineStr">
         <is>
           <t>Post-Development</t>
         </is>
       </c>
       <c r="B19" s="65" t="inlineStr">
         <is>
-          <t>WAF / signed widget token / captcha for public AI</t>
+          <t>Scaling tune (pool/concurrency/replicas) + CDN</t>
         </is>
       </c>
       <c r="C19" s="69" t="inlineStr">
         <is>
-          <t>Backend Dev</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="D19" s="69" t="inlineStr"/>
@@ -4352,45 +4788,45 @@
       <c r="H19" s="65" t="inlineStr"/>
     </row>
     <row r="20" ht="36" customHeight="1" s="52">
-      <c r="A20" s="84" t="inlineStr">
+      <c r="A20" s="100" t="inlineStr">
         <is>
           <t>Post-Development</t>
         </is>
       </c>
-      <c r="B20" s="81" t="inlineStr">
-        <is>
-          <t>Scaling tune (pool/concurrency/replicas) + CDN</t>
-        </is>
-      </c>
-      <c r="C20" s="82" t="inlineStr">
-        <is>
-          <t>DevOps</t>
-        </is>
-      </c>
-      <c r="D20" s="82" t="inlineStr"/>
-      <c r="E20" s="82" t="inlineStr"/>
-      <c r="F20" s="82" t="inlineStr"/>
-      <c r="G20" s="82" t="inlineStr">
+      <c r="B20" s="98" t="inlineStr">
+        <is>
+          <t>Hypercare monitoring &amp; SLA tracking (30 days)</t>
+        </is>
+      </c>
+      <c r="C20" s="99" t="inlineStr">
+        <is>
+          <t>Both Devs</t>
+        </is>
+      </c>
+      <c r="D20" s="99" t="inlineStr"/>
+      <c r="E20" s="99" t="inlineStr"/>
+      <c r="F20" s="99" t="inlineStr"/>
+      <c r="G20" s="99" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="H20" s="81" t="inlineStr"/>
+      <c r="H20" s="98" t="inlineStr"/>
     </row>
     <row r="21" ht="36" customHeight="1" s="52">
-      <c r="A21" s="84" t="inlineStr">
+      <c r="A21" s="100" t="inlineStr">
         <is>
           <t>Post-Development</t>
         </is>
       </c>
       <c r="B21" s="65" t="inlineStr">
         <is>
-          <t>Hypercare monitoring &amp; SLA tracking (30 days)</t>
+          <t>Background worker for reports/PDF + dead-letter syncs</t>
         </is>
       </c>
       <c r="C21" s="69" t="inlineStr">
         <is>
-          <t>Both Devs</t>
+          <t>Backend Dev</t>
         </is>
       </c>
       <c r="D21" s="69" t="inlineStr"/>
@@ -4404,30 +4840,34 @@
       <c r="H21" s="65" t="inlineStr"/>
     </row>
     <row r="22" ht="36" customHeight="1" s="52">
-      <c r="A22" s="84" t="inlineStr">
+      <c r="A22" s="100" t="inlineStr">
         <is>
           <t>Post-Development</t>
         </is>
       </c>
-      <c r="B22" s="81" t="inlineStr">
-        <is>
-          <t>Background worker for reports/PDF + dead-letter syncs</t>
-        </is>
-      </c>
-      <c r="C22" s="82" t="inlineStr">
-        <is>
-          <t>Backend Dev</t>
-        </is>
-      </c>
-      <c r="D22" s="82" t="inlineStr"/>
-      <c r="E22" s="82" t="inlineStr"/>
-      <c r="F22" s="82" t="inlineStr"/>
-      <c r="G22" s="82" t="inlineStr">
+      <c r="B22" s="98" t="inlineStr">
+        <is>
+          <t>CI/CD: staging gate + dependency/secret scanning</t>
+        </is>
+      </c>
+      <c r="C22" s="99" t="inlineStr">
+        <is>
+          <t>DevOps</t>
+        </is>
+      </c>
+      <c r="D22" s="99" t="inlineStr"/>
+      <c r="E22" s="99" t="inlineStr"/>
+      <c r="F22" s="99" t="inlineStr"/>
+      <c r="G22" s="99" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="H22" s="81" t="inlineStr"/>
+      <c r="H22" s="98" t="inlineStr">
+        <is>
+          <t>CI already on PRs</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4442,7 +4882,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4453,7 +4893,7 @@
   <cols>
     <col width="14" customWidth="1" style="52" min="1" max="1"/>
     <col width="50" customWidth="1" style="52" min="2" max="2"/>
-    <col width="60" customWidth="1" style="52" min="3" max="3"/>
+    <col width="58" customWidth="1" style="52" min="3" max="3"/>
     <col width="16" customWidth="1" style="52" min="4" max="5"/>
     <col width="20" customWidth="1" style="52" min="6" max="6"/>
     <col width="28" customWidth="1" style="52" min="7" max="7"/>
@@ -4504,148 +4944,148 @@
       </c>
     </row>
     <row r="3" ht="60" customHeight="1" s="52">
-      <c r="A3" s="85" t="inlineStr">
+      <c r="A3" s="83" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="B3" s="86" t="inlineStr">
+      <c r="B3" s="84" t="inlineStr">
         <is>
           <t>Breaks core money/data flow or takes the platform down; no workaround.</t>
         </is>
       </c>
-      <c r="C3" s="86" t="inlineStr">
-        <is>
-          <t>AI assistant 500s on every call; DB pool exhaustion outage; spoofed payment webhook; cross-tenant data leak.</t>
-        </is>
-      </c>
-      <c r="D3" s="87" t="inlineStr">
+      <c r="C3" s="84" t="inlineStr">
+        <is>
+          <t>AI assistant 500s on every call (now fixed); DB pool exhaustion; spoofed payment webhook; cross-tenant leak.</t>
+        </is>
+      </c>
+      <c r="D3" s="85" t="inlineStr">
         <is>
           <t>Immediate (&lt; 1 h)</t>
         </is>
       </c>
-      <c r="E3" s="87" t="inlineStr">
+      <c r="E3" s="85" t="inlineStr">
         <is>
           <t>4 h (same day)</t>
         </is>
       </c>
-      <c r="F3" s="87" t="inlineStr">
+      <c r="F3" s="85" t="inlineStr">
         <is>
           <t>Tech Lead</t>
         </is>
       </c>
-      <c r="G3" s="87" t="inlineStr">
+      <c r="G3" s="85" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1" s="52">
-      <c r="A4" s="88" t="inlineStr">
+      <c r="A4" s="86" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B4" s="89" t="inlineStr">
-        <is>
-          <t>Major feature broken or a real cost/abuse/security risk; workaround is painful.</t>
-        </is>
-      </c>
-      <c r="C4" s="89" t="inlineStr">
-        <is>
-          <t>Public AI chat cost abuse; 70B fallback doubling spend; no rate limit on auth routes; Redis SPOF.</t>
-        </is>
-      </c>
-      <c r="D4" s="90" t="inlineStr">
+      <c r="B4" s="87" t="inlineStr">
+        <is>
+          <t>Major feature broken or a real cost/abuse/security risk.</t>
+        </is>
+      </c>
+      <c r="C4" s="87" t="inlineStr">
+        <is>
+          <t>DB connection held during LLM; public AI abuse; Redis SPOF; no rate limit on authed routes.</t>
+        </is>
+      </c>
+      <c r="D4" s="88" t="inlineStr">
         <is>
           <t>2 h</t>
         </is>
       </c>
-      <c r="E4" s="90" t="inlineStr">
+      <c r="E4" s="88" t="inlineStr">
         <is>
           <t>24 h</t>
         </is>
       </c>
-      <c r="F4" s="90" t="inlineStr">
+      <c r="F4" s="88" t="inlineStr">
         <is>
           <t>Tech Lead</t>
         </is>
       </c>
-      <c r="G4" s="90" t="inlineStr">
+      <c r="G4" s="88" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1" s="52">
-      <c r="A5" s="91" t="inlineStr">
+      <c r="A5" s="89" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="B5" s="92" t="inlineStr">
-        <is>
-          <t>Degraded behaviour, performance, or hygiene issue; limited blast radius.</t>
-        </is>
-      </c>
-      <c r="C5" s="92" t="inlineStr">
-        <is>
-          <t>O(n*m) availability loops; PII at INFO; fragile provider detection; report memory spikes.</t>
-        </is>
-      </c>
-      <c r="D5" s="93" t="inlineStr">
+      <c r="B5" s="90" t="inlineStr">
+        <is>
+          <t>Degraded behaviour, performance or hygiene; limited blast radius.</t>
+        </is>
+      </c>
+      <c r="C5" s="90" t="inlineStr">
+        <is>
+          <t>Availability loops; SSE lifetime; PII at INFO (now fixed); provider detection.</t>
+        </is>
+      </c>
+      <c r="D5" s="91" t="inlineStr">
         <is>
           <t>4 h</t>
         </is>
       </c>
-      <c r="E5" s="93" t="inlineStr">
+      <c r="E5" s="91" t="inlineStr">
         <is>
           <t>3 business days</t>
         </is>
       </c>
-      <c r="F5" s="93" t="inlineStr">
+      <c r="F5" s="91" t="inlineStr">
         <is>
           <t>Tech Lead</t>
         </is>
       </c>
-      <c r="G5" s="93" t="inlineStr">
+      <c r="G5" s="91" t="inlineStr">
         <is>
           <t>Tech Lead</t>
         </is>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1" s="52">
-      <c r="A6" s="94" t="inlineStr">
+      <c r="A6" s="92" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="B6" s="95" t="inlineStr">
-        <is>
-          <t>Cosmetic, observability, or low-likelihood issue; fix when convenient.</t>
-        </is>
-      </c>
-      <c r="C6" s="95" t="inlineStr">
-        <is>
-          <t>Chart echo reliability; silent usage accounting; canned-error monitoring gap.</t>
-        </is>
-      </c>
-      <c r="D6" s="83" t="inlineStr">
+      <c r="B6" s="93" t="inlineStr">
+        <is>
+          <t>Cosmetic/observability/low-likelihood; fix when convenient.</t>
+        </is>
+      </c>
+      <c r="C6" s="93" t="inlineStr">
+        <is>
+          <t>Chart echo; usage accounting; canned-error alerting.</t>
+        </is>
+      </c>
+      <c r="D6" s="94" t="inlineStr">
         <is>
           <t>Next sprint</t>
         </is>
       </c>
-      <c r="E6" s="83" t="inlineStr">
+      <c r="E6" s="94" t="inlineStr">
         <is>
           <t>1–2 sprints</t>
         </is>
       </c>
-      <c r="F6" s="83" t="inlineStr">
+      <c r="F6" s="94" t="inlineStr">
         <is>
           <t>Tech Lead</t>
         </is>
       </c>
-      <c r="G6" s="83" t="inlineStr">
+      <c r="G6" s="94" t="inlineStr">
         <is>
           <t>Tech Lead</t>
         </is>
@@ -4658,12 +5098,12 @@
           <t>COLOUR LEGEND</t>
         </is>
       </c>
-      <c r="B9" s="74" t="n"/>
-      <c r="C9" s="74" t="n"/>
-      <c r="D9" s="74" t="n"/>
-      <c r="E9" s="74" t="n"/>
-      <c r="F9" s="74" t="n"/>
-      <c r="G9" s="75" t="n"/>
+      <c r="B9" s="95" t="n"/>
+      <c r="C9" s="95" t="n"/>
+      <c r="D9" s="95" t="n"/>
+      <c r="E9" s="95" t="n"/>
+      <c r="F9" s="95" t="n"/>
+      <c r="G9" s="96" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1" s="52">
       <c r="A10" s="28" t="inlineStr">
@@ -4711,7 +5151,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4748,13 +5188,13 @@
           <t>ISSUES BY STATUS</t>
         </is>
       </c>
-      <c r="B4" s="75" t="n"/>
+      <c r="B4" s="96" t="n"/>
       <c r="D4" s="60" t="inlineStr">
         <is>
           <t>ISSUES BY PRIORITY</t>
         </is>
       </c>
-      <c r="E4" s="75" t="n"/>
+      <c r="E4" s="96" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1" s="52">
       <c r="A5" s="34" t="inlineStr">
@@ -4898,7 +5338,7 @@
           <t>ISSUES BY PHASE</t>
         </is>
       </c>
-      <c r="B14" s="75" t="n"/>
+      <c r="B14" s="96" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1" s="52">
       <c r="A15" s="34" t="inlineStr">
@@ -4958,7 +5398,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4968,9 +5408,9 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" style="52" min="1" max="1"/>
-    <col width="34" customWidth="1" style="52" min="2" max="2"/>
-    <col width="10" customWidth="1" style="52" min="3" max="3"/>
-    <col width="20" customWidth="1" style="52" min="4" max="4"/>
+    <col width="32" customWidth="1" style="52" min="2" max="2"/>
+    <col width="11" customWidth="1" style="52" min="3" max="3"/>
+    <col width="18" customWidth="1" style="52" min="4" max="4"/>
     <col width="18" customWidth="1" style="52" min="5" max="5"/>
     <col width="26" customWidth="1" style="52" min="6" max="6"/>
   </cols>
@@ -5015,7 +5455,7 @@
       </c>
     </row>
     <row r="3" ht="44" customHeight="1" s="52">
-      <c r="A3" s="96" t="inlineStr">
+      <c r="A3" s="101" t="inlineStr">
         <is>
           <t>Pre-Development</t>
         </is>
@@ -5025,19 +5465,19 @@
           <t>Architecture/cost-governance gap</t>
         </is>
       </c>
-      <c r="C3" s="85" t="inlineStr">
+      <c r="C3" s="83" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
       <c r="D3" s="65" t="inlineStr">
         <is>
-          <t>Design review / audit</t>
+          <t>Design review</t>
         </is>
       </c>
       <c r="E3" s="65" t="inlineStr">
         <is>
-          <t>Before dev starts</t>
+          <t>Before dev</t>
         </is>
       </c>
       <c r="F3" s="65" t="inlineStr">
@@ -5047,39 +5487,39 @@
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" s="52">
-      <c r="A4" s="96" t="inlineStr">
+      <c r="A4" s="101" t="inlineStr">
         <is>
           <t>Pre-Development</t>
         </is>
       </c>
-      <c r="B4" s="81" t="inlineStr">
+      <c r="B4" s="98" t="inlineStr">
         <is>
           <t>Capacity/connection planning</t>
         </is>
       </c>
-      <c r="C4" s="88" t="inlineStr">
+      <c r="C4" s="86" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D4" s="81" t="inlineStr">
-        <is>
-          <t>Load test / review</t>
-        </is>
-      </c>
-      <c r="E4" s="81" t="inlineStr">
+      <c r="D4" s="98" t="inlineStr">
+        <is>
+          <t>Load test</t>
+        </is>
+      </c>
+      <c r="E4" s="98" t="inlineStr">
         <is>
           <t>Before go-live</t>
         </is>
       </c>
-      <c r="F4" s="81" t="inlineStr">
-        <is>
-          <t>Sets the scaling ceiling</t>
+      <c r="F4" s="98" t="inlineStr">
+        <is>
+          <t>Sets scaling ceiling</t>
         </is>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" s="52">
-      <c r="A5" s="96" t="inlineStr">
+      <c r="A5" s="101" t="inlineStr">
         <is>
           <t>Pre-Development</t>
         </is>
@@ -5089,7 +5529,7 @@
           <t>Trusted-proxy / IP trust</t>
         </is>
       </c>
-      <c r="C5" s="88" t="inlineStr">
+      <c r="C5" s="86" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -5111,39 +5551,39 @@
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" s="52">
-      <c r="A6" s="96" t="inlineStr">
+      <c r="A6" s="101" t="inlineStr">
         <is>
           <t>Pre-Development</t>
         </is>
       </c>
-      <c r="B6" s="81" t="inlineStr">
+      <c r="B6" s="98" t="inlineStr">
         <is>
           <t>Team/ownership gap</t>
         </is>
       </c>
-      <c r="C6" s="91" t="inlineStr">
+      <c r="C6" s="89" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D6" s="81" t="inlineStr">
-        <is>
-          <t>Management review</t>
-        </is>
-      </c>
-      <c r="E6" s="81" t="inlineStr">
+      <c r="D6" s="98" t="inlineStr">
+        <is>
+          <t>Mgmt review</t>
+        </is>
+      </c>
+      <c r="E6" s="98" t="inlineStr">
         <is>
           <t>This quarter</t>
         </is>
       </c>
-      <c r="F6" s="81" t="inlineStr">
+      <c r="F6" s="98" t="inlineStr">
         <is>
           <t>Staffing decision</t>
         </is>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" s="52">
-      <c r="A7" s="94" t="inlineStr">
+      <c r="A7" s="92" t="inlineStr">
         <is>
           <t>Development</t>
         </is>
@@ -5153,7 +5593,7 @@
           <t>AI agent crash / 500</t>
         </is>
       </c>
-      <c r="C7" s="85" t="inlineStr">
+      <c r="C7" s="83" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -5165,426 +5605,426 @@
       </c>
       <c r="E7" s="65" t="inlineStr">
         <is>
-          <t>&lt; 1 day</t>
+          <t>&lt; 1 day (DONE)</t>
         </is>
       </c>
       <c r="F7" s="65" t="inlineStr">
         <is>
-          <t>Feature-down bug</t>
+          <t>Was feature-down; fixed</t>
         </is>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" s="52">
-      <c r="A8" s="94" t="inlineStr">
+      <c r="A8" s="92" t="inlineStr">
         <is>
           <t>Development</t>
         </is>
       </c>
-      <c r="B8" s="81" t="inlineStr">
+      <c r="B8" s="98" t="inlineStr">
         <is>
           <t>Connection held during LLM</t>
         </is>
       </c>
-      <c r="C8" s="88" t="inlineStr">
+      <c r="C8" s="86" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D8" s="81" t="inlineStr">
+      <c r="D8" s="98" t="inlineStr">
         <is>
           <t>Load test / profiling</t>
         </is>
       </c>
-      <c r="E8" s="81" t="inlineStr">
+      <c r="E8" s="98" t="inlineStr">
         <is>
           <t>1 sprint</t>
         </is>
       </c>
-      <c r="F8" s="81" t="inlineStr">
+      <c r="F8" s="98" t="inlineStr">
         <is>
           <t>Scaling root cause</t>
         </is>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" s="52">
-      <c r="A9" s="94" t="inlineStr">
+      <c r="A9" s="92" t="inlineStr">
         <is>
           <t>Development</t>
         </is>
       </c>
       <c r="B9" s="65" t="inlineStr">
         <is>
-          <t>Prompt injection / authz on tools</t>
-        </is>
-      </c>
-      <c r="C9" s="91" t="inlineStr">
+          <t>Prompt injection / tool authz</t>
+        </is>
+      </c>
+      <c r="C9" s="89" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D9" s="65" t="inlineStr">
+        <is>
+          <t>Security test</t>
+        </is>
+      </c>
+      <c r="E9" s="65" t="inlineStr">
+        <is>
+          <t>&lt; 1 sprint</t>
+        </is>
+      </c>
+      <c r="F9" s="65" t="inlineStr">
+        <is>
+          <t>Money/data at risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1" s="52">
+      <c r="A10" s="92" t="inlineStr">
+        <is>
+          <t>Development</t>
+        </is>
+      </c>
+      <c r="B10" s="98" t="inlineStr">
+        <is>
+          <t>Performance (loops/N+1)</t>
+        </is>
+      </c>
+      <c r="C10" s="92" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D10" s="98" t="inlineStr">
+        <is>
+          <t>Profiling</t>
+        </is>
+      </c>
+      <c r="E10" s="98" t="inlineStr">
+        <is>
+          <t>1-2 sprints</t>
+        </is>
+      </c>
+      <c r="F10" s="98" t="inlineStr">
+        <is>
+          <t>Latency under load</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1" s="52">
+      <c r="A11" s="92" t="inlineStr">
+        <is>
+          <t>Development</t>
+        </is>
+      </c>
+      <c r="B11" s="65" t="inlineStr">
+        <is>
+          <t>Cost (model/fallback)</t>
+        </is>
+      </c>
+      <c r="C11" s="86" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D11" s="65" t="inlineStr">
+        <is>
+          <t>Cost review</t>
+        </is>
+      </c>
+      <c r="E11" s="65" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F11" s="65" t="inlineStr">
+        <is>
+          <t>Fixed: cheap fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1" s="52">
+      <c r="A12" s="92" t="inlineStr">
+        <is>
+          <t>Development</t>
+        </is>
+      </c>
+      <c r="B12" s="98" t="inlineStr">
+        <is>
+          <t>Privacy/logging hygiene</t>
+        </is>
+      </c>
+      <c r="C12" s="83" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D12" s="98" t="inlineStr">
+        <is>
+          <t>Code review</t>
+        </is>
+      </c>
+      <c r="E12" s="98" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F12" s="98" t="inlineStr">
+        <is>
+          <t>Fixed: PII to DEBUG</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="1" s="52">
+      <c r="A13" s="102" t="inlineStr">
+        <is>
+          <t>Post-Development</t>
+        </is>
+      </c>
+      <c r="B13" s="65" t="inlineStr">
+        <is>
+          <t>Pool exhaustion / outage</t>
+        </is>
+      </c>
+      <c r="C13" s="83" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="D9" s="65" t="inlineStr">
+      <c r="D13" s="65" t="inlineStr">
+        <is>
+          <t>Monitoring/alert</t>
+        </is>
+      </c>
+      <c r="E13" s="65" t="inlineStr">
+        <is>
+          <t>Immediate (&lt;1h)</t>
+        </is>
+      </c>
+      <c r="F13" s="65" t="inlineStr">
+        <is>
+          <t>Hypercare SLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1" s="52">
+      <c r="A14" s="102" t="inlineStr">
+        <is>
+          <t>Post-Development</t>
+        </is>
+      </c>
+      <c r="B14" s="98" t="inlineStr">
+        <is>
+          <t>Payment webhook integrity</t>
+        </is>
+      </c>
+      <c r="C14" s="83" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="D14" s="98" t="inlineStr">
         <is>
           <t>Security test</t>
         </is>
       </c>
-      <c r="E9" s="65" t="inlineStr">
+      <c r="E14" s="98" t="inlineStr">
+        <is>
+          <t>Immediate</t>
+        </is>
+      </c>
+      <c r="F14" s="98" t="inlineStr">
+        <is>
+          <t>Financial loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1" s="52">
+      <c r="A15" s="102" t="inlineStr">
+        <is>
+          <t>Post-Development</t>
+        </is>
+      </c>
+      <c r="B15" s="65" t="inlineStr">
+        <is>
+          <t>Abuse / DoS / cost spike</t>
+        </is>
+      </c>
+      <c r="C15" s="86" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D15" s="65" t="inlineStr">
+        <is>
+          <t>Monitoring/WAF</t>
+        </is>
+      </c>
+      <c r="E15" s="65" t="inlineStr">
+        <is>
+          <t>&lt; 24h</t>
+        </is>
+      </c>
+      <c r="F15" s="65" t="inlineStr">
+        <is>
+          <t>Cost + availability</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44" customHeight="1" s="52">
+      <c r="A16" s="102" t="inlineStr">
+        <is>
+          <t>Post-Development</t>
+        </is>
+      </c>
+      <c r="B16" s="98" t="inlineStr">
+        <is>
+          <t>Cost monitoring/alerting</t>
+        </is>
+      </c>
+      <c r="C16" s="89" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D16" s="98" t="inlineStr">
+        <is>
+          <t>Dashboards</t>
+        </is>
+      </c>
+      <c r="E16" s="98" t="inlineStr">
+        <is>
+          <t>1-2 sprints</t>
+        </is>
+      </c>
+      <c r="F16" s="98" t="inlineStr">
+        <is>
+          <t>Late detection</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="44" customHeight="1" s="52">
+      <c r="A17" s="102" t="inlineStr">
+        <is>
+          <t>Post-Development</t>
+        </is>
+      </c>
+      <c r="B17" s="65" t="inlineStr">
+        <is>
+          <t>Redis HA / SPOF</t>
+        </is>
+      </c>
+      <c r="C17" s="86" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D17" s="65" t="inlineStr">
+        <is>
+          <t>Infra review</t>
+        </is>
+      </c>
+      <c r="E17" s="65" t="inlineStr">
         <is>
           <t>&lt; 1 sprint</t>
         </is>
       </c>
-      <c r="F9" s="65" t="inlineStr">
-        <is>
-          <t>Money/data at risk</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="44" customHeight="1" s="52">
-      <c r="A10" s="94" t="inlineStr">
-        <is>
-          <t>Development</t>
-        </is>
-      </c>
-      <c r="B10" s="81" t="inlineStr">
-        <is>
-          <t>Performance (N+1 / loops)</t>
-        </is>
-      </c>
-      <c r="C10" s="94" t="inlineStr">
+      <c r="F17" s="65" t="inlineStr">
+        <is>
+          <t>Multi-control failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="44" customHeight="1" s="52">
+      <c r="A18" s="102" t="inlineStr">
+        <is>
+          <t>Post-Development</t>
+        </is>
+      </c>
+      <c r="B18" s="98" t="inlineStr">
+        <is>
+          <t>External dependency failure</t>
+        </is>
+      </c>
+      <c r="C18" s="89" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D10" s="81" t="inlineStr">
-        <is>
-          <t>Profiling</t>
-        </is>
-      </c>
-      <c r="E10" s="81" t="inlineStr">
+      <c r="D18" s="98" t="inlineStr">
+        <is>
+          <t>Retries/alerts</t>
+        </is>
+      </c>
+      <c r="E18" s="98" t="inlineStr">
         <is>
           <t>1-2 sprints</t>
         </is>
       </c>
-      <c r="F10" s="81" t="inlineStr">
-        <is>
-          <t>Latency under load</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="44" customHeight="1" s="52">
-      <c r="A11" s="94" t="inlineStr">
-        <is>
-          <t>Development</t>
-        </is>
-      </c>
-      <c r="B11" s="65" t="inlineStr">
-        <is>
-          <t>Cost (model choice / fallback)</t>
-        </is>
-      </c>
-      <c r="C11" s="88" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D11" s="65" t="inlineStr">
-        <is>
-          <t>Cost review</t>
-        </is>
-      </c>
-      <c r="E11" s="65" t="inlineStr">
-        <is>
-          <t>1 sprint</t>
-        </is>
-      </c>
-      <c r="F11" s="65" t="inlineStr">
-        <is>
-          <t>Direct bill impact</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="44" customHeight="1" s="52">
-      <c r="A12" s="94" t="inlineStr">
-        <is>
-          <t>Development</t>
-        </is>
-      </c>
-      <c r="B12" s="81" t="inlineStr">
-        <is>
-          <t>Privacy/logging hygiene</t>
-        </is>
-      </c>
-      <c r="C12" s="85" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D12" s="81" t="inlineStr">
-        <is>
-          <t>Code review</t>
-        </is>
-      </c>
-      <c r="E12" s="81" t="inlineStr">
-        <is>
-          <t>1-2 sprints</t>
-        </is>
-      </c>
-      <c r="F12" s="81" t="inlineStr">
-        <is>
-          <t>Compliance</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="44" customHeight="1" s="52">
-      <c r="A13" s="97" t="inlineStr">
+      <c r="F18" s="98" t="inlineStr">
+        <is>
+          <t>Data loss/UX</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="44" customHeight="1" s="52">
+      <c r="A19" s="102" t="inlineStr">
         <is>
           <t>Post-Development</t>
         </is>
       </c>
-      <c r="B13" s="65" t="inlineStr">
-        <is>
-          <t>Production outage / pool exhaustion</t>
-        </is>
-      </c>
-      <c r="C13" s="85" t="inlineStr">
+      <c r="B19" s="65" t="inlineStr">
+        <is>
+          <t>Tenant isolation regression</t>
+        </is>
+      </c>
+      <c r="C19" s="83" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="D13" s="65" t="inlineStr">
-        <is>
-          <t>Monitoring / alert</t>
-        </is>
-      </c>
-      <c r="E13" s="65" t="inlineStr">
-        <is>
-          <t>Immediate (&lt;1h)</t>
-        </is>
-      </c>
-      <c r="F13" s="65" t="inlineStr">
-        <is>
-          <t>Hypercare SLA</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="44" customHeight="1" s="52">
-      <c r="A14" s="97" t="inlineStr">
+      <c r="D19" s="65" t="inlineStr">
+        <is>
+          <t>Security test</t>
+        </is>
+      </c>
+      <c r="E19" s="65" t="inlineStr">
+        <is>
+          <t>Immediate</t>
+        </is>
+      </c>
+      <c r="F19" s="65" t="inlineStr">
+        <is>
+          <t>Data breach</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="44" customHeight="1" s="52">
+      <c r="A20" s="102" t="inlineStr">
         <is>
           <t>Post-Development</t>
         </is>
       </c>
-      <c r="B14" s="81" t="inlineStr">
-        <is>
-          <t>Payment webhook integrity</t>
-        </is>
-      </c>
-      <c r="C14" s="85" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="D14" s="81" t="inlineStr">
-        <is>
-          <t>Security test</t>
-        </is>
-      </c>
-      <c r="E14" s="81" t="inlineStr">
-        <is>
-          <t>Immediate</t>
-        </is>
-      </c>
-      <c r="F14" s="81" t="inlineStr">
-        <is>
-          <t>Financial loss</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="44" customHeight="1" s="52">
-      <c r="A15" s="97" t="inlineStr">
-        <is>
-          <t>Post-Development</t>
-        </is>
-      </c>
-      <c r="B15" s="65" t="inlineStr">
-        <is>
-          <t>Abuse / DoS / cost spike</t>
-        </is>
-      </c>
-      <c r="C15" s="88" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D15" s="65" t="inlineStr">
-        <is>
-          <t>Monitoring / WAF</t>
-        </is>
-      </c>
-      <c r="E15" s="65" t="inlineStr">
-        <is>
-          <t>&lt; 24h</t>
-        </is>
-      </c>
-      <c r="F15" s="65" t="inlineStr">
-        <is>
-          <t>Cost + availability</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="44" customHeight="1" s="52">
-      <c r="A16" s="97" t="inlineStr">
-        <is>
-          <t>Post-Development</t>
-        </is>
-      </c>
-      <c r="B16" s="81" t="inlineStr">
-        <is>
-          <t>Cost monitoring/alerting</t>
-        </is>
-      </c>
-      <c r="C16" s="91" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D16" s="81" t="inlineStr">
-        <is>
-          <t>Dashboards</t>
-        </is>
-      </c>
-      <c r="E16" s="81" t="inlineStr">
-        <is>
-          <t>1-2 sprints</t>
-        </is>
-      </c>
-      <c r="F16" s="81" t="inlineStr">
-        <is>
-          <t>Late detection</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="44" customHeight="1" s="52">
-      <c r="A17" s="97" t="inlineStr">
-        <is>
-          <t>Post-Development</t>
-        </is>
-      </c>
-      <c r="B17" s="65" t="inlineStr">
-        <is>
-          <t>Redis HA / SPOF</t>
-        </is>
-      </c>
-      <c r="C17" s="88" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D17" s="65" t="inlineStr">
-        <is>
-          <t>Infra review</t>
-        </is>
-      </c>
-      <c r="E17" s="65" t="inlineStr">
-        <is>
-          <t>&lt; 1 sprint</t>
-        </is>
-      </c>
-      <c r="F17" s="65" t="inlineStr">
-        <is>
-          <t>Multi-control failure</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="44" customHeight="1" s="52">
-      <c r="A18" s="97" t="inlineStr">
-        <is>
-          <t>Post-Development</t>
-        </is>
-      </c>
-      <c r="B18" s="81" t="inlineStr">
-        <is>
-          <t>External dependency failure</t>
-        </is>
-      </c>
-      <c r="C18" s="91" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D18" s="81" t="inlineStr">
-        <is>
-          <t>Retries/alerts</t>
-        </is>
-      </c>
-      <c r="E18" s="81" t="inlineStr">
-        <is>
-          <t>1-2 sprints</t>
-        </is>
-      </c>
-      <c r="F18" s="81" t="inlineStr">
-        <is>
-          <t>Data loss/UX</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="44" customHeight="1" s="52">
-      <c r="A19" s="97" t="inlineStr">
-        <is>
-          <t>Post-Development</t>
-        </is>
-      </c>
-      <c r="B19" s="65" t="inlineStr">
-        <is>
-          <t>Tenant isolation regression</t>
-        </is>
-      </c>
-      <c r="C19" s="85" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="D19" s="65" t="inlineStr">
-        <is>
-          <t>Security test</t>
-        </is>
-      </c>
-      <c r="E19" s="65" t="inlineStr">
-        <is>
-          <t>Immediate</t>
-        </is>
-      </c>
-      <c r="F19" s="65" t="inlineStr">
-        <is>
-          <t>Data breach</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="44" customHeight="1" s="52">
-      <c r="A20" s="97" t="inlineStr">
-        <is>
-          <t>Post-Development</t>
-        </is>
-      </c>
-      <c r="B20" s="81" t="inlineStr">
+      <c r="B20" s="98" t="inlineStr">
         <is>
           <t>Observability gaps</t>
         </is>
       </c>
-      <c r="C20" s="94" t="inlineStr">
+      <c r="C20" s="92" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D20" s="81" t="inlineStr">
+      <c r="D20" s="98" t="inlineStr">
         <is>
           <t>Metrics</t>
         </is>
       </c>
-      <c r="E20" s="81" t="inlineStr">
+      <c r="E20" s="98" t="inlineStr">
         <is>
           <t>Next sprint</t>
         </is>
       </c>
-      <c r="F20" s="81" t="inlineStr">
+      <c r="F20" s="98" t="inlineStr">
         <is>
           <t>Slow detection</t>
         </is>
@@ -5598,7 +6038,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
